--- a/public/files/CHR/camp_situations.xlsx
+++ b/public/files/CHR/camp_situations.xlsx
@@ -436,14 +436,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,12 +467,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>②反応</t>
+          <t>②A 友好度高</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>③朝</t>
+          <t>②B 付き合い薄い</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>②C 悪態</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>③A 疲れなし</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>③B 疲れ残り</t>
         </is>
       </c>
     </row>
@@ -484,17 +502,32 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>……雨、漏ってる。……場所、変えよう</t>
+          <t>……雨漏ってる……場所変えるかな…</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>……乾いてる場所、探そう</t>
+          <t>この程度なら、気にせず眠れると思う</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>……昨日は、大変だった。……朝で、よかった</t>
+          <t>場所を変えれば、大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>こんな水浸しの場所で……眠れるわけない</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……昨日の雨漏り、なんとか凌げたな</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……昨日の雨漏り、なんとか凌げたな。それに、あまり眠れなかった気がする</t>
         </is>
       </c>
     </row>
@@ -509,17 +542,32 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>……風、入ってくる。……寒い</t>
+          <t>……どこかから風が入ってくる。……寒い…</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>……何か、詰めよう。布とか</t>
+          <t>この程度の風なら、平気だ</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>……朝。……夜は、ずっと寒かった</t>
+          <t>隙間を塞げば、大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>凍えそうだ……こんなの、耐えられない</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……夜は少し寒かったな</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……夜は少し寒かったな。それに、あまり眠れなかった気がする</t>
         </is>
       </c>
     </row>
@@ -534,17 +582,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>……床、傾いてる。……転がりそう</t>
+          <t>…うーん…床が傾いてる。…落ち着かないな…</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>……何か、下に敷こう</t>
+          <t>この程度の傾きなら、平気だ</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>……朝。……何回か、転がった気がする</t>
+          <t>壁側なら、安定すると思う</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>このままだと、転がり落ちる……怖い</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……何度か転がった気がする</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……何度か転がった気がする。それに、あまり眠れなかった気がする</t>
         </is>
       </c>
     </row>
@@ -559,17 +622,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>……真っ暗。……何も、見えない</t>
+          <t>…もう真っ暗だ…。何も見えないな…</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>……声、かけあおう。はぐれないように</t>
+          <t>この程度の暗さなら、慣れれば平気だ</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>……朝。……明るくて、ほっとする</t>
+          <t>声をかけあえば、大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>何も見えない……怖い</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……明るくて、少し安心する</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……明るくて、少し安心する。それに、あまり眠れなかった気がする</t>
         </is>
       </c>
     </row>
@@ -584,17 +662,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>……変な匂い。……我慢、しないと</t>
+          <t>…なんだか変な匂いがする…</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>……離れた場所、探そう</t>
+          <t>ちょっと匂うけど、平気だ</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>……朝。……匂い、少し慣れた気がする</t>
+          <t>離れた場所に移れば、大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>こんな臭い場所で……一晩なんて、耐えられない</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……匂い、少しは慣れた気がする</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……匂い、少しは慣れた気がする。それに、あまり眠れなかった気がする</t>
         </is>
       </c>
     </row>
@@ -609,17 +702,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>……石、当たってる。……痛い</t>
+          <t>…どこも石がゴロゴロしてるな…</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>……どかした方がいい、と思う</t>
+          <t>この程度なら、平気だ</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>……朝。……背中、少し痛い</t>
+          <t>どければ、大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>背骨、折れそう……痛すぎる</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……背中、少し痛いな</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……背中、少し痛いな。それに、あまり眠れなかった気がする</t>
         </is>
       </c>
     </row>
@@ -634,17 +742,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>……脚、伸ばせない。……窮屈</t>
+          <t>…うう…狭くて脚が伸ばせない…</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>……横向きなら、少し楽かも</t>
+          <t>この程度の狭さなら、平気だ</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>……朝。……脚、まだ縮こまってる</t>
+          <t>横向きなら、少し楽かもしれない</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>脚が、攣りそう……動けなくなる</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……脚、まだ少し固まってるな</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……脚、まだ少し固まってるな。それに、あまり眠れなかった気がする</t>
         </is>
       </c>
     </row>
@@ -659,17 +782,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>……床、冷たい。……眠れない</t>
+          <t>…床が冷たい…</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>……上着、下に敷こう</t>
+          <t>この程度なら、平気だ</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>……朝。……体、まだ冷たい</t>
+          <t>何か敷けば、少しマシになると思う</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>凍え死んじゃう……こんなの、無理だ</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……体、まだ少し冷たいな</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……体、まだ少し冷たいな。それに、あまり眠れなかった気がする</t>
         </is>
       </c>
     </row>
@@ -684,17 +822,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>……蜘蛛の巣。……絡まった</t>
+          <t>…うぺっ、蜘蛛の巣が…</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>……払っておく。……大丈夫</t>
+          <t>この程度なら、平気だ</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>……朝。……髪に、まだついてないか心配</t>
+          <t>払えば、大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>気持ち悪い……眠れる気がしない</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……髪、確認しておこう</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……髪、確認しておこう。それに、あまり眠れなかった気がする</t>
         </is>
       </c>
     </row>
@@ -709,17 +862,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>……埃っぽい。……くしゃみ、出そう</t>
+          <t>…うう…埃っぽい…</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>……大丈夫? ……布、口に当てて</t>
+          <t>この程度なら、平気だ</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>……朝。……くしゃみ、少し落ち着いた</t>
+          <t>口を覆えば、少しマシになると思う</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>くしゃみ、止まらない……辛い</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……くしゃみ、落ち着いてきたな</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……くしゃみ、落ち着いてきたな。それに、あまり眠れなかった気がする</t>
         </is>
       </c>
     </row>
@@ -734,17 +902,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>……今の、声……気のせい、かな</t>
+          <t>…？…今の…声…？　…気のせいかな…</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>……大丈夫。……近くにいるから</t>
+          <t>気のせいだと思う、平気だ</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>……朝。……あの声、もう聞こえない</t>
+          <t>近くにいれば、大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>本気で、怖い……これ</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……あの声、もう聞こえないな</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……あの声、もう聞こえないな。それに、あまり眠れなかった気がする</t>
         </is>
       </c>
     </row>
@@ -759,17 +942,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>……さっき、虫が……顔の近く、通った</t>
+          <t>……うっ、虫が……顔の上通った！</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>……気にしない方が、いいと思う</t>
+          <t>この程度なら、平気だ</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>……朝。……もう、虫はいない、みたい</t>
+          <t>気にしなければ、大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>鳥肌、立った……眠れない</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……もう虫はいないみたいだ</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……もう虫はいないみたいだ。それに、あまり眠れなかった気がする</t>
         </is>
       </c>
     </row>
@@ -784,17 +982,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>……見られてる、気がする</t>
+          <t>……なんだか…なにか見られてる気がして落ち着かないな…</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>……気のせい、だといいけど。気をつけよう</t>
+          <t>気のせいだと思う、平気だ</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>……朝。……あの気配、もうしない</t>
+          <t>気をつけていれば、大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>生きた心地が、しない……これ</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……あの気配、もうしないな</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……あの気配、もうしないな。それに、あまり眠れなかった気がする</t>
         </is>
       </c>
     </row>
@@ -809,17 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>……さっきから、同じ音が……気になる</t>
+          <t>……さっきから何度も同じ音が……気になる…</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>……危険な音、ではなさそう。……たぶん</t>
+          <t>気にならない、平気だ</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>……朝。……あの音、止まってる</t>
+          <t>建物の音だと思う、大丈夫だ</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>気になって……全然、眠れない</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……あの音、止まってるな</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……あの音、止まってるな。それに、あまり眠れなかった気がする</t>
         </is>
       </c>
     </row>
@@ -834,17 +1062,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>……鏡、割れてない。……珍しい</t>
+          <t>……割れてない鏡があるな、珍しいな…</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>……自分の顔、久しぶりに見た気がする</t>
+          <t>珍しいだけだと思う、平気だ</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>……朝。……もう一回、鏡、見てみようかな</t>
+          <t>気にしなければ、大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>不気味だ……眠れないかもしれない</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……また鏡、見てみようかな</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……また鏡、見てみようかな。それに、あまり眠れなかった気がする</t>
         </is>
       </c>
     </row>
@@ -859,17 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>……見張り、誰から……決めよう</t>
+          <t>……何か気配を感じるな…隠れてれば大丈夫かな</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>……順番、決まったなら、それで大丈夫</t>
+          <t>交代で見張りしよう。私が最初でもいい</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>……朝。……見張り、無事に終わった</t>
+          <t>順番を決めた方がいいかもしれない</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>見張りは、あまり得意じゃないな</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……見張り、問題なくできたな</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……あまり、眠れなかったな</t>
         </is>
       </c>
     </row>
@@ -884,17 +1142,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>……これ、みんなの分……ちゃんと、分けないと</t>
+          <t>……ああ…今日は何食べようかな…</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>……私の分は、少なくていい</t>
+          <t>これくらいで、平気だ</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>……朝。……みんな、ちゃんと食べられたかな</t>
+          <t>均等に分ければ、大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>こんなに少ないと……お腹が空いて、辛い</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……みんな、ちゃんと食べられたかな</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……みんな、ちゃんと食べられたかな。それに、あまり眠れなかった気がする</t>
         </is>
       </c>
     </row>
@@ -909,17 +1182,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>……声、小さくしないと</t>
+          <t>……静かだな、物音立てないように気をつけないとな…</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>……うん。……気をつける</t>
+          <t>この程度なら、平気だ</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>……朝。……もう、声、抑えなくていい</t>
+          <t>気をつければ、大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>ずっと小声なのは……息が詰まる</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……もう、声を抑えなくていいな</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……もう、声を抑えなくていいな。それに、あまり眠れなかった気がする</t>
         </is>
       </c>
     </row>
@@ -934,17 +1222,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>……平らな場所、狭い……どうしよう</t>
+          <t>……今日は特に寒いな……どうしよう</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>……私、座って寝るから、大丈夫</t>
+          <t>この程度の寒さなら、平気だ</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>……朝。……あったかかった、気がする</t>
+          <t>くっつけば、暖かいと思う</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>凍えそうだ……これじゃ、眠れない</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……昨日は、あったかかった気がする</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……昨日は、あったかかった気がする。それに、あまり眠れなかった気がする</t>
         </is>
       </c>
     </row>
@@ -959,17 +1262,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>……ここ、綺麗……珍しい</t>
+          <t>……この部屋いいね…ここに住もうかな…</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>……でも、少し、警戒はしておこう</t>
+          <t>少し綺麗、という程度だと思う</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>……朝。……結局、何もなかった。よかった</t>
+          <t>綺麗な部屋で、良かったと思う</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>出来すぎてる……何かあるのかもしれない</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……結局、何もなかったな。よかった</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>朝か。……結局、何もなかったな。よかった。それに、あまり眠れなかった気がする</t>
         </is>
       </c>
     </row>
@@ -984,14 +1302,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1012,12 +1333,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>②反応</t>
+          <t>②A 友好度高</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>③朝</t>
+          <t>②B 付き合い薄い</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>②C 悪態</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>③A 疲れなし</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>③B 疲れ残り</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1373,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>……仕方あるまい、こちらに寄るがいい</t>
+          <t>……この程度の雨、我には心地よいくらいだが</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>……場所を変えれば済む話だろう</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>……このような水浸しの場所で夜を明かすなど、人の子には酷というものだな</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>……ふん、あの程度の雨音、我には子守唄だったがな</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>……ふん、あの程度の雨音、我には子守唄だったがな。珍しく、体が重いと感じるな</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1413,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>……ふん、手間のかかることだ。貸してみろ</t>
+          <t>……この程度の風、我には涼しいくらいだが</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>……隙間を塞げば済む話だろう</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>……この寒さで一晩とは、人の子には酷というものだな</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>……あの程度の風、我には涼を取る程度のものだったが</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>……あの程度の風、我には涼を取る程度のものだったが。珍しく、体が重いと感じるな</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1453,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>……そこの壁に寄るがいい。多少はマシだろう</t>
+          <t>……この程度の傾き、我には気にもならぬが</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>……壁に寄れば済む話だろう</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>……このような不安定な足場で眠るとは、人の子には酷なことよ</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>……多少の傾き程度、我にはどうということもないが</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>……多少の傾き程度、我にはどうということもないが。珍しく、体が重いと感じるな</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1493,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>……我の側にいれば、迷うことはあるまい</t>
+          <t>……闇など、我には気にもならぬが</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>……声を掛け合えば済む話だろう</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>……この暗闇の中で一晩とは、人の子には酷なことよ</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>……闇も悪くはないが、光も嫌いではないぞ</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>……闇も悪くはないが、光も嫌いではないぞ。珍しく、体が重いと感じるな</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1533,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>……我のそばにいれば、気にもならぬだろうよ</t>
+          <t>……この程度の匂い、我には気にもならぬが</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>……離れれば済む話だろう</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>……このような悪臭の中で夜を明かすなど、人の子には酷というものだな</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>……匂い程度、我には最初から気にもならぬが</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>……匂い程度、我には最初から気にもならぬが。珍しく、体が重いと感じるな</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1573,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>……面倒だな。まあ、退けてやろう</t>
+          <t>……この程度の石、我には枕のようなものだが</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>……どければ済む話だろう</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>……このような硬い床で一晩とは、人の子には酷というものだな</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>……石で痛むとは、まだまだ鍛錬が足りぬな</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>……石で痛むとは、まだまだ鍛錬が足りぬな。珍しく、体が重いと感じるな</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1613,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>……体を丸めておけ。それで十分だろう</t>
+          <t>……この程度の狭さ、我には気にもならぬが</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>……体を丸めれば済む話だろう</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>……このような手狭な場所で夜を明かすなど、人の子には酷というものだな</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>……この程度の窮屈さ、我には障りもないが</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>……この程度の窮屈さ、我には障りもないが。珍しく、体が重いと感じるな</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1653,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>……我の外套でも使うがいい。無駄にはすまい</t>
+          <t>……この程度の冷たさ、我には心地よいくらいだが</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>……何か敷けば済む話だろう</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>……この冷たさで一晩とは、人の子には酷というものだな</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>……冷えなど、我にはむしろ心地よいものだが</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>……冷えなど、我にはむしろ心地よいものだが。珍しく、体が重いと感じるな</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1693,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>……我が払ってやろう。造作もない</t>
+          <t>……蜘蛛の巣程度、我には無縁のものだが</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>……払えば済む話だろう</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>……このような不潔な場所で夜を明かすなど、人の子には酷というものだな</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>……蜘蛛の巣程度、我の美しさを損なうことはない</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>……蜘蛛の巣程度、我の美しさを損なうことはない。珍しく、体が重いと感じるな</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1733,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>……仕方ない奴だな。これで、我慢しておけ</t>
+          <t>……埃程度、我のくしゃみを誘うことはないが</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>……口を覆えば済む話だろう</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>……このような埃まみれの場所で夜を明かすなど、人の子には酷というものだな</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>……埃程度、我を煩わせることはないがな</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>……埃程度、我を煩わせることはないがな。珍しく、体が重いと感じるな</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1773,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>……案ずるな。我がいる限り、容易には近づけまい</t>
+          <t>……この程度の声、我には子守唄のようなものだが</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>……我のそばにいれば済む話だろう</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>……この声、少々厄介な気配を纏っているな……油断はできぬ</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>……あの程度の声、気にするだけ無駄だったろう</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>……あの程度の声、気にするだけ無駄だったろう。珍しく、体が重いと感じるな</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1813,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>……気にするな。我が近くにいれば、寄りつきもすまい</t>
+          <t>……虫程度、我には塵にも等しいものだが</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>……気にせねば済む話だろう</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>……このような小さきものに怯えるとは、人の子は面倒なものだな</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>……虫如き、我にはどうでもよいことだが</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>……虫如き、我にはどうでもよいことだが。珍しく、体が重いと感じるな</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1853,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>……何であれ、我が主に手出しはさせぬがな</t>
+          <t>……この程度の視線、我には無いも同然だが</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>……我が警戒しておけば済む話だろう</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>……ふん、この気配、只者ではないな……油断はできぬ</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>……あの程度の視線、脅威にすらならぬがな</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>……あの程度の視線、脅威にすらならぬがな。珍しく、体が重いと感じるな</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1893,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>……脅威であれば、我がとうに気づいている</t>
+          <t>……この程度の音、我には子守唄にもならぬが</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>……建物の軋みだろう。気にするほどではない</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>……この音、只者の建物の音とは思えぬな……不気味だ</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>……あの程度の音、気にするまでもなかったな</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>……あの程度の音、気にするまでもなかったな。珍しく、体が重いと感じるな</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1933,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>……我の美しさ、少しも損なわれておらぬな</t>
+          <t>……鏡が割れておらぬ程度、我には興味の対象にもならぬが</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>……気にせねば済む話だろう</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>……ふん、この鏡、少々気に食わぬ気配を纏っているな</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>……朝の光でも、我の美しさは変わらぬな</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>……朝の光でも、我の美しさは変わらぬな。珍しく、体が重いと感じるな</t>
         </is>
       </c>
     </row>
@@ -1407,17 +1968,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>……見張りなど、我一人で十分だと思うがな</t>
+          <t>……この程度、隠れずとも問題ないがな</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>……好きにするがいい。我は、いつでも起きていられる</t>
+          <t>……交代など不要だ。我が見張っていてやる</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>……見張りなど、我にはさしたる負担でもないがな</t>
+          <t>……順番か。好きに決めるがいい</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>……見張りなど、我にやらせておけばいいものを</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>……見張り程度、我には造作もないことだったな</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>……珍しく、眠気を感じるな。この体は、存外正直だ</t>
         </is>
       </c>
     </row>
@@ -1432,17 +2008,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>……我の分は、後でいい。人の子から先にせよ</t>
+          <t>……何か、腹の足しになるものはあるか</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>……我の分は不要だと言っている。人の子を優先せよ</t>
+          <t>……この程度、我には無くとも構わぬが</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>……均等に分ければ済む話だろう</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>……このような乏しい配給とは……人の子には酷というものだな</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>……人の子に分け与えるのも、悪くない気分だったな</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>……人の子に分け与えるのも、悪くない気分だったな。珍しく、体が重いと感じるな</t>
         </is>
       </c>
     </row>
@@ -1457,17 +2048,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>……この程度の会話、我には囁きにも聞こえぬが</t>
+          <t>……音程度、我には気にする必要もないが</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>……分かった分かった。うるさくはせんよ</t>
+          <t>……この程度、我には囁きにも聞こえぬが</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>……気をつければ済む話だろう</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>……ずっと囁くとは……人の子には窮屈なことよ</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>……もう、囁く必要もないか。窮屈だったな</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>……もう、囁く必要もないか。窮屈だったな。珍しく、体が重いと感じるな</t>
         </is>
       </c>
     </row>
@@ -1482,17 +2088,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>……我にくっつけば、暖かいぞ。遠慮するな</t>
+          <t>……この程度の寒さ、我には涼しいだけだがな</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>……我のそばに来い。暖を分けてやろう</t>
+          <t>……この程度の寒さ、我には涼しいくらいだが</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>……我にくっつけば、すぐ暖まるぞ</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>……この寒さで一晩とは、人の子には酷というものだな</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>……あたたかかっただろう。我のそばは、いつでも歓迎だぞ</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>……あたたかかっただろう。我のそばは、いつでも歓迎だぞ。珍しく、体が重いと感じるな</t>
         </is>
       </c>
     </row>
@@ -1512,12 +2133,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>……罠でなければいいがな。……まあ、今夜は楽しむとしよう</t>
+          <t>……まあ、悪くない部屋だな</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>……悪くない部屋を見つけたものだな</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>……出来すぎだな……罠でなければ良いがな</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>……ふん、何もない方が、退屈ではあるがな</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>……ふん、何もない方が、退屈ではあるがな。珍しく、体が重いと感じるな</t>
         </is>
       </c>
     </row>
@@ -1532,14 +2168,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1560,12 +2199,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>②反応</t>
+          <t>②A 友好度高</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>③朝</t>
+          <t>②B 付き合い薄い</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>②C 悪態</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>③A 疲れなし</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>③B 疲れ残り</t>
         </is>
       </c>
     </row>
@@ -1585,12 +2239,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>こちらへどうぞ……乾いてるところ、探しましょう</t>
+          <t>これくらいなら、大丈夫だと思うわ</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>場所を変えれば、大丈夫だと思うわ</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>こんなに濡れた場所で……さすがに、辛いわね……</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>朝ね……昨日の雨の音、なかなか寝付けなかったわ</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>朝ね……昨日の雨の音、なかなか寝付けなかったわ。まだ、少し眠いわ</t>
         </is>
       </c>
     </row>
@@ -1610,12 +2279,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>これで塞ぎましょう……少しは暖かくなるはずよ</t>
+          <t>この程度なら、大丈夫だと思うわ</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>隙間を塞げば、大丈夫だと思うわ</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>凍えそうだわ……さすがに、これは辛いわね……</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>朝ね……昨日は、少し冷えたわ</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>朝ね……昨日は、少し冷えたわ。まだ、少し眠いわ</t>
         </is>
       </c>
     </row>
@@ -1635,12 +2319,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>壁の近くの方が、安心かもしれないわね</t>
+          <t>この程度なら、大丈夫だと思うわ</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>壁側の方が、安定すると思うわ</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>転がり落ちてしまいそうだわ……これは、危ないわね……</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>朝ね……昨日、何度か転がってしまったわ</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>朝ね……昨日、何度か転がってしまったわ。まだ、少し眠いわ</t>
         </is>
       </c>
     </row>
@@ -1660,12 +2359,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>手を繋いでおきましょうか。安心すると思うわ</t>
+          <t>この程度なら、大丈夫だと思うわ</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>声をかけあえば、大丈夫だと思うわ</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>何も見えないわ……これは、さすがに怖いわね……</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>朝ね……明るくなって、少し安心したわ</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>朝ね……明るくなって、少し安心したわ。まだ、少し眠いわ</t>
         </is>
       </c>
     </row>
@@ -1685,12 +2399,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>こちらの方が、少し楽かもしれないわ</t>
+          <t>ちょっと匂うけど、大丈夫だと思うわ</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>離れた場所に移れば、大丈夫だと思うわ</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>こんなに匂う場所で一晩なんて……さすがに、辛いわね……</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>朝ね……匂い、少しは慣れた気がするわ</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>朝ね……匂い、少しは慣れた気がするわ。まだ、少し眠いわ</t>
         </is>
       </c>
     </row>
@@ -1710,12 +2439,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>どかしましょう……そのままだと、辛いものね</t>
+          <t>この程度なら、大丈夫だと思うわ</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>どければ、大丈夫だと思うわ</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>背中が、折れそうだわ……これは、さすがに痛いわね……</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>朝ね……背中、少し痛いわ</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>朝ね……背中、少し痛いわ。まだ、少し眠いわ</t>
         </is>
       </c>
     </row>
@@ -1735,12 +2479,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>横向きにすると、少し楽になるかもしれないわ</t>
+          <t>この程度なら、大丈夫だと思うわ</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>横向きだと、少し楽かもしれないわ</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>脚が、攣ってしまいそうだわ……これは、さすがに辛いわね……</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>朝ね……脚、少し固まってしまったわ</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>朝ね……脚、少し固まってしまったわ。まだ、少し眠いわ</t>
         </is>
       </c>
     </row>
@@ -1760,12 +2519,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>これを敷きましょう……少し、暖かくなるはずよ</t>
+          <t>この程度なら、大丈夫だと思うわ</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>何か敷けば、少し楽になると思うわ</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>凍えてしまいそうだわ……さすがに、これは辛いわね……</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>朝ね……体、まだ少し冷えているわ</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>朝ね……体、まだ少し冷えているわ。まだ、少し眠いわ</t>
         </is>
       </c>
     </row>
@@ -1785,12 +2559,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>払っておきますね……大丈夫よ</t>
+          <t>この程度なら、大丈夫だと思うわ</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>払えば、大丈夫だと思うわ</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>うっ……これは、さすがに気持ち悪くて眠れないかもしれないわ</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>朝ね……髪、確認しておきましょう</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>朝ね……髪、確認しておきましょう。まだ、少し眠いわ</t>
         </is>
       </c>
     </row>
@@ -1810,12 +2599,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>大丈夫かしら……これ、使ってちょうだい</t>
+          <t>この程度なら、大丈夫だと思うわ</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>口を覆えば、少し楽になると思うわ</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>くしゃみが、止まらないわ……これは、さすがに辛いわね……。へくちっ</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>朝ね……くしゃみ、少し落ち着いたわ。……へくちっ</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>朝ね……くしゃみ、少し落ち着いたわ。……へくちっ。まだ、少し眠いわ</t>
         </is>
       </c>
     </row>
@@ -1835,12 +2639,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>大丈夫よ……わたしたち、一緒にいるから</t>
+          <t>気のせいだと思うわ、大丈夫よ</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>近くにいれば、大丈夫だと思うわ</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>本気で、怖いわ……これは、さすがに……</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>朝ね……昨日の声、もう聞こえないわ</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>朝ね……昨日の声、もう聞こえないわ。まだ、少し眠いわ</t>
         </is>
       </c>
     </row>
@@ -1860,12 +2679,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>大丈夫よ……きっと、驚いただけだと思うわ</t>
+          <t>この程度なら、大丈夫だと思うわ</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>気にしなければ、大丈夫だと思うわ</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>鳥肌が……これは、さすがに眠れないかもしれないわ</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>朝ね……虫、もういないみたいね</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>朝ね……虫、もういないみたいね。まだ、少し眠いわ</t>
         </is>
       </c>
     </row>
@@ -1885,12 +2719,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>気をつけましょう……何もないと、いいけれど</t>
+          <t>気のせいだと思うわ、大丈夫よ</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>気をつければ、大丈夫だと思うわ</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>生きた心地がしないわ……これは、さすがに……</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>朝ね……あの気配、もう感じないわ</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>朝ね……あの気配、もう感じないわ。まだ、少し眠いわ</t>
         </is>
       </c>
     </row>
@@ -1910,12 +2759,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>きっと、建物の音ね……大丈夫だと思うわ</t>
+          <t>この程度なら、大丈夫だと思うわ</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>建物の音だと思うわ、大丈夫よ</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>気になって、眠れないわ……これは、さすがに……</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>朝ね……あの音、止まっているわ</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>朝ね……あの音、止まっているわ。まだ、少し眠いわ</t>
         </is>
       </c>
     </row>
@@ -1935,12 +2799,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>久しぶりに、自分の顔を見たわ……不思議な気持ち</t>
+          <t>珍しいだけだと思うわ、大丈夫よ</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>気にしなければ、大丈夫だと思うわ</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>なんだか、不気味だわ……これは、さすがに眠れないかも……</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>朝ね……また鏡、見てみましょうか</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>朝ね……また鏡、見てみましょうか。まだ、少し眠いわ</t>
         </is>
       </c>
     </row>
@@ -1955,17 +2834,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>見張りの順番、決めましょうか……わたし、いつでも平気よ</t>
+          <t>静かにしていれば、大丈夫かしら</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>その順番で大丈夫よ……お互い様だもの</t>
+          <t>交代でいたしましょうか。わたし、最初でも大丈夫よ</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>朝ね……見張り、無事に終わったわ</t>
+          <t>順番、決めておきましょうか……</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>見張り……正直、少し苦手だわ</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>朝ね……見張り、問題なくできたわ</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>朝ね……あまり眠れなくて、少し眠いわ</t>
         </is>
       </c>
     </row>
@@ -1980,17 +2874,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>みんなの分、ちゃんと分けましょうね……少し、緊張するわ</t>
+          <t>何を、食べましょうかしら</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>わたしは少しでいいわ……みんな、しっかり食べて</t>
+          <t>これくらいで、大丈夫だと思うわ</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>均等に分ければ、大丈夫だと思うわ</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>こんなに少ないと……お腹、すいてしまうわ……</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>朝ね……みんな、ちゃんと食べられたかしら</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>朝ね……みんな、ちゃんと食べられたかしら。まだ、少し眠いわ</t>
         </is>
       </c>
     </row>
@@ -2005,17 +2914,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>静かに、お話しましょうね……</t>
+          <t>物音、気をつけないと……</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>ええ、気をつけるわ</t>
+          <t>この程度なら、大丈夫だと思うわ</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>気をつければ、大丈夫だと思うわ</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>ずっと小声だと……なんだか、息が詰まるわ……</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>朝ね……もう、普通の声で大丈夫ね</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>朝ね……もう、普通の声で大丈夫ね。まだ、少し眠いわ</t>
         </is>
       </c>
     </row>
@@ -2030,17 +2954,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>平らな場所、狭いわね……くっつきましょうか</t>
+          <t>寒いわね……何か、暖まる方法探しましょうか</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>くっついても……いいかしら……？</t>
+          <t>この程度なら、大丈夫だと思うわ</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>くっつけば、暖かいと思うわ</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>凍えそうだわ……これは、さすがに眠れないわね……</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>朝ね……昨日は、あたたかく眠れたわ</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>朝ね……昨日は、あたたかく眠れたわ。まだ、少し眠いわ</t>
         </is>
       </c>
     </row>
@@ -2060,12 +2999,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>嬉しいけれど……念のため、気をつけましょうね</t>
+          <t>ちょっと綺麗な部屋ね</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>綺麗な部屋で、良かったわ</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>出来すぎだわ……何か、あるかもしれないわね……</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>朝ね……結局、何もなかったわ。よかった</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>朝ね……結局、何もなかったわ。よかった。まだ、少し眠いわ</t>
         </is>
       </c>
     </row>
@@ -2080,14 +3034,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2108,12 +3065,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>②反応</t>
+          <t>②A 友好度高</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>③朝</t>
+          <t>②B 付き合い薄い</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>②C 悪態</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>③A 疲れなし</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>③B 疲れ残り</t>
         </is>
       </c>
     </row>
@@ -2133,12 +3105,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>こっち空いてるよ、移ってきて</t>
+          <t>このくらいの雨漏りなら、へっちゃらだよ!</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>場所変えれば大丈夫だと思うよ</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>えっ、こんな水浸しの場所で寝るの!? さすがに厳しくない!?</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>朝だ……昨日の雨漏り、ちゃんと避けられてよかった</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>朝だ……昨日の雨漏り、ちゃんと避けられてよかった。あと、なんか体がだるい気がする</t>
         </is>
       </c>
     </row>
@@ -2158,12 +3145,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>これ、隙間に詰めてみようか</t>
+          <t>この程度の風、全然平気だよ!</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>隙間塞げば大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これ凍えて死んじゃうんじゃ!? さすがに寒すぎない!?</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>朝だ……昨日の風、結構冷えたね</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>朝だ……昨日の風、結構冷えたね。あと、なんか体がだるい気がする</t>
         </is>
       </c>
     </row>
@@ -2183,12 +3185,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>この辺、平らかも。ここにしよう</t>
+          <t>この程度の傾き、余裕だよ!</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>壁側なら安定すると思う</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これ寝てる間に転がり落ちない!? 危なくない!?</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>朝だ……昨日、何回か転がっちゃった気がする</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>朝だ……昨日、何回か転がっちゃった気がする。あと、なんか体がだるい気がする</t>
         </is>
       </c>
     </row>
@@ -2208,12 +3225,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>みんな、声出して。位置確認しよう</t>
+          <t>この程度の暗さ、平気だよ!</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>声かけあえば大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これ本当に何も見えない!? 怖すぎない!?</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>朝だ! 明るくなると、なんか安心するね</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 明るくなると、なんか安心するね。あと、なんか体がだるい気がする</t>
         </is>
       </c>
     </row>
@@ -2233,12 +3265,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>あっちの方が、少しマシかも。移動しよう</t>
+          <t>ちょっと匂うけど、平気だよ!</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>離れた場所に移れば大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>えっ、こんな臭い場所で一晩過ごすの!? さすがにキツくない!?</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>朝だ……昨日の匂い、寝てる間に慣れちゃったかも</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>朝だ……昨日の匂い、寝てる間に慣れちゃったかも。あと、なんか体がだるい気がする</t>
         </is>
       </c>
     </row>
@@ -2258,12 +3305,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>貸して、私がどかすよ</t>
+          <t>この程度の石、平気だよ!</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>どければ大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これ背骨折れそうなんだけど!? 痛すぎない!?</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>朝だ……背中、ちょっと痛い気がする</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>朝だ……背中、ちょっと痛い気がする。あと、なんか体がだるい気がする</t>
         </is>
       </c>
     </row>
@@ -2283,12 +3345,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>横向きで寝ると、少し伸ばせるかもよ</t>
+          <t>この程度の狭さ、平気だよ!</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>横向きなら少し楽になるかも</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これ脚攣って動けなくなりそうなんだけど!?</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>朝だ……脚、ちょっと固まっちゃったかも</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>朝だ……脚、ちょっと固まっちゃったかも。あと、なんか体がだるい気がする</t>
         </is>
       </c>
     </row>
@@ -2308,12 +3385,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>これ、下に敷いて。少しはマシになるよ</t>
+          <t>この程度の冷たさ、平気だよ!</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>何か敷けば少しマシになると思う</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これ凍死しちゃうんじゃ!? さすがに冷たすぎない!?</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>朝だ……体、まだちょっと冷えてる気がする</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>朝だ……体、まだちょっと冷えてる気がする。あと、なんか体がだるい気がする</t>
         </is>
       </c>
     </row>
@@ -2333,12 +3425,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>払っておくね、任せて</t>
+          <t>この程度の蜘蛛の巣、平気だよ!</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>払えば大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これ気持ち悪すぎて眠れないよ!?</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>朝だ! 髪、蜘蛛の巣ついてないかチェックしないと</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 髪、蜘蛛の巣ついてないかチェックしないと。あと、なんか体がだるい気がする</t>
         </is>
       </c>
     </row>
@@ -2358,12 +3465,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>大丈夫? 布、口に当てておくといいよ</t>
+          <t>この程度の埃、平気だよ!</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>口を覆えば少しマシになると思う</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>えっ、くしゃみ止まらないんだけど!? これキツくない!?</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>朝だ! くしゃみ、だいぶ落ち着いたよ</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! くしゃみ、だいぶ落ち着いたよ。あと、なんか体がだるい気がする</t>
         </is>
       </c>
     </row>
@@ -2383,12 +3505,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>大丈夫、みんなここにいるから</t>
+          <t>気のせいだよ、平気平気!</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>近くにいれば大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>えっ、今の本気で怖いんだけど!?</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>朝だ……昨日の声、朝になったら聞こえないね</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>朝だ……昨日の声、朝になったら聞こえないね。あと、なんか体がだるい気がする</t>
         </is>
       </c>
     </row>
@@ -2408,12 +3545,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>気にしない方がいいよ、たぶん無害だから</t>
+          <t>この程度の虫、平気だよ!</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>気にしなければ大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>えっ、鳥肌立って眠れないんだけど!?</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>朝だ! 昨日の虫、もういないみたいだね</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 昨日の虫、もういないみたいだね。あと、なんか体がだるい気がする</t>
         </is>
       </c>
     </row>
@@ -2433,12 +3585,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>気をつけながら、様子見よう</t>
+          <t>気のせいだよ、平気平気!</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>気をつければ大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これ生きた心地しないんだけど!?</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>朝だ……昨日の気配、朝になったら感じないね</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>朝だ……昨日の気配、朝になったら感じないね。あと、なんか体がだるい気がする</t>
         </is>
       </c>
     </row>
@@ -2458,12 +3625,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>たぶん、建物のきしみだと思う。大丈夫だよ</t>
+          <t>この程度の音、平気だよ!</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>建物の音だと思う、大丈夫だよ</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これ気になって全然眠れないんだけど!?</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>朝だ! 昨日の音、朝は止まってるね</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 昨日の音、朝は止まってるね。あと、なんか体がだるい気がする</t>
         </is>
       </c>
     </row>
@@ -2483,12 +3665,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>久しぶりに、自分の顔見た気がするよ</t>
+          <t>珍しいだけだよ、平気平気!</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>気にしなければ大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これなんか不気味すぎて眠れないんだけど!?</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>朝だ! もう一回鏡見てみようかな</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! もう一回鏡見てみようかな。あと、なんか体がだるい気がする</t>
         </is>
       </c>
     </row>
@@ -2503,17 +3700,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>見張りの順番、決めようか。じゃんけんとか?</t>
+          <t>静かにしていれば、大丈夫だと思う</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>決まった順番で大丈夫だよ、みんなで協力しよう</t>
+          <t>交代でやろっか! 私、最初やるよ</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>朝だ! 見張り、みんな無事に終えられたね</t>
+          <t>順番、決めておこうか</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>正直、見張り眠くなっちゃうんだよね……</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 見張り、ちゃんとこなせたよ</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>朝だ……見張りのせいか、あんまり寝れなかったかも</t>
         </is>
       </c>
     </row>
@@ -2528,17 +3740,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>みんなに、ちゃんと均等に分けようね</t>
+          <t>何食べようかな、これ</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>私は少なめで平気だよ、みんな優先して</t>
+          <t>これくらいで平気だよ!</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>均等に分ければ大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これだけしかないの!? さすがに少なすぎない!?</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>朝だ! みんな、ちゃんと食べられたかな</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! みんな、ちゃんと食べられたかな。あと、なんか体がだるい気がする</t>
         </is>
       </c>
     </row>
@@ -2553,17 +3780,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>静かに話そうね、声抑えて</t>
+          <t>物音、気をつけないとね</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>了解、気をつけるね</t>
+          <t>この程度、平気だよ!</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>気をつければ大丈夫だと思う</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>えっ、ずっと小声なのキツくない!? 息詰まりそう!</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>朝だ! もう普通の声で話せるね</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! もう普通の声で話せるね。あと、なんか体がだるい気がする</t>
         </is>
       </c>
     </row>
@@ -2578,17 +3820,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>平らな場所狭いね……くっついた方がいいかな</t>
+          <t>寒いね……何か暖まる方法ないかな</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>私は平気、隅で座って寝るよ</t>
+          <t>この程度の寒さ、平気だよ!</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>くっつけば暖かいと思うよ</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これ凍えて眠れないんだけど!?</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>朝だ……昨日、意外とあったかく眠れた気がする</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>朝だ……昨日、意外とあったかく眠れた気がする。あと、なんか体がだるい気がする</t>
         </is>
       </c>
     </row>
@@ -2608,12 +3865,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>ラッキーだけど、一応警戒はしておこうか</t>
+          <t>ちょっと綺麗な部屋だね、程度かな</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>綺麗な部屋で良かったよ</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これ出来すぎてない!? 絶対なんかあるよ!</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>朝だ! 結局何もなかったね、よかった</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 結局何もなかったね、よかった。あと、なんか体がだるい気がする</t>
         </is>
       </c>
     </row>
@@ -2628,14 +3900,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2656,12 +3931,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>②反応</t>
+          <t>②A 友好度高</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>③朝</t>
+          <t>②B 付き合い薄い</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>②C 悪態</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>③A 疲れなし</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>③B 疲れ残り</t>
         </is>
       </c>
     </row>
@@ -2681,12 +3971,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>しゃーねえ、あたしんとこ来いよ</t>
+          <t>これくらいの雨漏り、屁でもねえよ</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>場所変えりゃいいだけだろ</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? こんなびしゃびしゃの場所で寝ろってのか、正気かよ</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>あー、あの雨漏り、うるさくて全然寝れなかったわ</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>あー、あの雨漏り、うるさくて全然寝れなかったわ。つーか、眠みぃ。寝足りねえわ</t>
         </is>
       </c>
     </row>
@@ -2706,12 +4011,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>布切れでも詰めときゃ多少マシだろ</t>
+          <t>この程度の風、屁でもねえわ</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>隙間塞ぎゃいいだろ</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? 凍え死ぬぐらい寒いんだけど、どうにかしろよ</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>さっむ……あの隙間風のせいで全然寝れなかったわ</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>さっむ……あの隙間風のせいで全然寝れなかったわ。つーか、眠みぃ。寝足りねえわ</t>
         </is>
       </c>
     </row>
@@ -2731,12 +4051,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>壁側に寝りゃ転がんねえだろ、多分</t>
+          <t>この程度、屁でもねえわ</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>壁側に寝りゃ安定するだろ</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? こんなん寝てる間に転落死するレベルだろ</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>あー、あの傾いた床のせいで、変な体勢で寝ちまったわ</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>あー、あの傾いた床のせいで、変な体勢で寝ちまったわ。つーか、眠みぃ。寝足りねえわ</t>
         </is>
       </c>
     </row>
@@ -2756,12 +4091,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>はぐれんなよ、暗いんだから</t>
+          <t>この程度の暗さ、屁でもねえわ</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>声かけあってりゃ平気だろ</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? マジで何も見えねえじゃん、これヤバくねえか</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>朝かよ、よかった……真っ暗なのはやっぱ苦手だわ</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>朝かよ、よかった……真っ暗なのはやっぱ苦手だわ。つーか、眠みぃ。寝足りねえわ</t>
         </is>
       </c>
     </row>
@@ -2781,12 +4131,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>鼻栓でもすっか、こんなん</t>
+          <t>ちょっと匂うくらい、屁でもねえわ</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>離れりゃいいだけだろ</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? こんな臭い場所で一晩過ごせってのか、勘弁してくれよ</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>朝か……あの匂い、結局最後まで気になったわ</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>朝か……あの匂い、結局最後まで気になったわ。つーか、眠みぃ。寝足りねえわ</t>
         </is>
       </c>
     </row>
@@ -2806,12 +4171,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>どかしゃいいだろ、それくらい</t>
+          <t>この程度、屁でもねえわ</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>どけりゃいいだけだろ</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? 背骨イカれそうなくらい痛いんだけど、マジかよ</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>あー、背中痛ってぇ……あの石のせいだな、絶対</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>あー、背中痛ってぇ……あの石のせいだな、絶対。つーか、眠みぃ。寝足りねえわ</t>
         </is>
       </c>
     </row>
@@ -2831,12 +4211,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>横向きで丸まってりゃ、多少マシだろ</t>
+          <t>この程度、屁でもねえわ</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>横向きなりゃ多少マシだろ</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? 脚攣って動けなくなりそうなんだけど、勘弁してくれ</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>あー、脚攣りそう……あの狭さのせいだわ</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>あー、脚攣りそう……あの狭さのせいだわ。つーか、眠みぃ。寝足りねえわ</t>
         </is>
       </c>
     </row>
@@ -2856,12 +4251,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>上着でも敷いとけ、少しはマシだろ</t>
+          <t>この程度、屁でもねえわ</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>何か敷きゃマシだろ</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? 芯まで凍えるくらい冷たいんだけど、どうにかしろよ</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>さっむ……あの床のせいで芯まで冷えたわ</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>さっむ……あの床のせいで芯まで冷えたわ。つーか、眠みぃ。寝足りねえわ</t>
         </is>
       </c>
     </row>
@@ -2881,12 +4291,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>貸せ、あたしが払ってやるよ</t>
+          <t>この程度、屁でもねえわ</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>払やいいだけだろ</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>うっわ、キモすぎ! こんなん払っても払っても切りねえじゃん</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>朝か……髪、蜘蛛の巣まみれになってないだろうな</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>朝か……髪、蜘蛛の巣まみれになってないだろうな。つーか、眠みぃ。寝足りねえわ</t>
         </is>
       </c>
     </row>
@@ -2906,12 +4331,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>うるせぇくしゃみだな……ほら、布貸してやるよ</t>
+          <t>この程度、屁でもねえわ</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>口塞ぎゃマシだろ</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>はぁ、くしゃみ止まんねえんだけど! 埃っぺぇんだよ、ここ</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>朝か……昨日のくしゃみ、ようやく収まったわ</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>朝か……昨日のくしゃみ、ようやく収まったわ。つーか、眠みぃ。寝足りねえわ</t>
         </is>
       </c>
     </row>
@@ -2931,12 +4371,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>大丈夫だ、あたしがいるから安心しろ</t>
+          <t>気のせいだろ、屁でもねえわ</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>近くにいりゃ平気だろ</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? 今の本気でヤバくねえか、マジで怖いんだけど</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>朝か……昨日の声、結局なんだったんだろうな</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>朝か……昨日の声、結局なんだったんだろうな。つーか、眠みぃ。寝足りねえわ</t>
         </is>
       </c>
     </row>
@@ -2956,12 +4411,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>気にすんな、虫くらい。あたしが払ってやるよ</t>
+          <t>この程度、屁でもねえわ</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>気にしなきゃ平気だろ</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>うっわ、鳥肌やば! 眠れねえんだけど、マジで</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>朝か……昨日の虫、もうどっか行ったみたいだな</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>朝か……昨日の虫、もうどっか行ったみたいだな。つーか、眠みぃ。寝足りねえわ</t>
         </is>
       </c>
     </row>
@@ -2981,12 +4451,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>気のせいならいいけどな、一応気をつけとけ</t>
+          <t>気のせいだろ、屁でもねえわ</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>気をつけてりゃ平気だろ</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? マジで見られてる気しかしねえんだけど、無理だろこれ</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>朝か……昨日の視線、もう感じねえな</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>朝か……昨日の視線、もう感じねえな。つーか、眠みぃ。寝足りねえわ</t>
         </is>
       </c>
     </row>
@@ -3006,12 +4491,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>多分ただの建物の音だろ、気にすんな</t>
+          <t>この程度、屁でもねえわ</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>建物の音だろ、平気だろ</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? あの音マジでうるせぇんだけど、眠れねえよ</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>朝か……あの音、うるさかったけど止まったな</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>朝か……あの音、うるさかったけど止まったな。つーか、眠みぃ。寝足りねえわ</t>
         </is>
       </c>
     </row>
@@ -3031,12 +4531,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>うわ、自分の顔久しぶりに見たわ……ボロボロじゃん</t>
+          <t>珍しいだけだろ、屁でもねえわ</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>気にしなきゃ平気だろ</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>うっわ、なんか不気味すぎんだけど、これ呪われてねえか</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>朝か……もっかい鏡見てみるか</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>朝か……もっかい鏡見てみるか。つーか、眠みぃ。寝足りねえわ</t>
         </is>
       </c>
     </row>
@@ -3051,17 +4566,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>見張り誰からやんの、あたしは別に後でいいけど</t>
+          <t>じっとしてりゃ、まあバレねえだろ</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>まあ、決まったんならそれでいいだろ</t>
+          <t>交代しようぜ、あたし最初やってやるよ</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>朝か……見張り、なんとか乗り切ったな</t>
+          <t>……まあ、順番くらいは決めとくか</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>見張りとか、正直だりぃんだけど</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>朝か……見張り、余裕だったわ</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>あー、眠み……見張りのせいで全然寝足りねえわ</t>
         </is>
       </c>
     </row>
@@ -3076,17 +4606,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>分け方でモメんのだりぃな……適当でいいだろ、別に</t>
+          <t>何か食い物ねえかな</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>あたしは平気だから、他の奴に多めにやれよ</t>
+          <t>これくらいで平気だろ、余裕だわ</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>均等に分けりゃいいだろ</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? こんだけしかねえのかよ、腹減りすぎて死ぬわ</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>朝か……昨日の分け方、あれでよかったんかな</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>朝か……昨日の分け方、あれでよかったんかな。つーか、眠みぃ。寝足りねえわ</t>
         </is>
       </c>
     </row>
@@ -3101,17 +4646,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>こそこそ喋んのも疲れんだよな、正直</t>
+          <t>物音、立てねえようにしねえとな</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>わーってるよ、そんくらい</t>
+          <t>この程度、屁でもねえわ</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>気をつけてりゃ平気だろ</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>はぁ、ずっとヒソヒソとか息苦しいんだけど、勘弁してくれ</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>朝か……やっと普通の声出せるわ</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>朝か……やっと普通の声出せるわ。つーか、眠みぃ。寝足りねえわ</t>
         </is>
       </c>
     </row>
@@ -3126,17 +4686,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>平らな場所せまっ……くっつくしかねえのか、これ</t>
+          <t>さっみぃ……なんか暖まる方法ねえかな</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>あたしは平気、適当に丸まって寝るから</t>
+          <t>この程度、屁でもねえわ</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>くっつきゃ暖かいだろ</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? 凍え死ぬくらい寒いんだけど、マジで</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>朝か……くっつくのも、悪くなかったな、あれ</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>朝か……くっつくのも、悪くなかったな、あれ。つーか、眠みぃ。寝足りねえわ</t>
         </is>
       </c>
     </row>
@@ -3156,12 +4731,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>出来すぎてて逆に怖いけどな、こういうの</t>
+          <t>まあまあ綺麗じゃん、程度だな</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>綺麗な部屋でラッキーだったな</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? 出来すぎだろ、これ絶対裏あるって</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>朝か……結局何もなかったな、拍子抜けだわ</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>朝か……結局何もなかったな、拍子抜けだわ。つーか、眠みぃ。寝足りねえわ</t>
         </is>
       </c>
     </row>
@@ -3176,14 +4766,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3204,12 +4797,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>②反応</t>
+          <t>②A 友好度高</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>③朝</t>
+          <t>②B 付き合い薄い</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>②C 悪態</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>③A 疲れなし</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>③B 疲れ残り</t>
         </is>
       </c>
     </row>
@@ -3229,12 +4837,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>こちらへどうぞ。……濡れておりませんわ</t>
+          <t>……この程度でしたら、問題ございませんわ</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>……場所を変えれば、大丈夫でしょう</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>……このような水浸しの場所で一晩とは……正気の沙汰とは思えませんわ</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>……昨夜の雨音、なかなか眠れませんでしたわ</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>……昨夜の雨音、なかなか眠れませんでしたわ。それに、まだ、眠気が残っておりますわ</t>
         </is>
       </c>
     </row>
@@ -3254,12 +4877,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>こちらの布を、お使いになってくださいませ</t>
+          <t>……この程度の風でしたら、問題ございませんわ</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>……隙間を塞げば、大丈夫でしょう</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>……凍えてしまいそうですわ……このような寒さ、耐えられません</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>……昨夜の風、随分と冷えましたわね</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>……昨夜の風、随分と冷えましたわね。それに、まだ、眠気が残っておりますわ</t>
         </is>
       </c>
     </row>
@@ -3279,12 +4917,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>壁際の方が、安定するかもしれませんわ</t>
+          <t>……この程度の傾きでしたら、問題ございませんわ</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>……壁際の方が、安定するでしょう</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>……このままでは、転がり落ちてしまいますわ……危険すぎます</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>……昨夜は、何度か体が傾きましたわね</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>……昨夜は、何度か体が傾きましたわね。それに、まだ、眠気が残っておりますわ</t>
         </is>
       </c>
     </row>
@@ -3304,12 +4957,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>お声を、かけ合いましょう。……はぐれては大変ですわ</t>
+          <t>……この程度の暗さでしたら、問題ございませんわ</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>……お声をかけ合えば、大丈夫でしょう</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>……何も見えませんわ……このような暗闇、恐ろしゅうございます</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>……朝ですのね。……明るいと、安心いたしますわ</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>……朝ですのね。……明るいと、安心いたしますわ。それに、まだ、眠気が残っておりますわ</t>
         </is>
       </c>
     </row>
@@ -3329,12 +4997,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>こちらへどうぞ。少し、匂いが和らぎますわ</t>
+          <t>……少々匂いますが、この程度でしたら、問題ございませんわ</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>……離れた場所に、移れば大丈夫でしょう</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>……このような悪臭の中で一晩とは……正気の沙汰とは思えませんわ</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>……朝ですわね。……匂いには、少し慣れましたけれど</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>……朝ですわね。……匂いには、少し慣れましたけれど。それに、まだ、眠気が残っておりますわ</t>
         </is>
       </c>
     </row>
@@ -3354,12 +5037,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>お手伝いいたしますわ。……こちら、どかしましょう</t>
+          <t>……この程度でしたら、問題ございませんわ</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>……どければ、大丈夫でしょう</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>……背骨が、折れてしまいそうですわ……これは酷うございます</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>……朝ですわね。……背中が、少し痛みますわ</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>……朝ですわね。……背中が、少し痛みますわ。それに、まだ、眠気が残っておりますわ</t>
         </is>
       </c>
     </row>
@@ -3379,12 +5077,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>横を向かれると、少し楽になるかもしれませんわ</t>
+          <t>……この程度でしたら、問題ございませんわ</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>……横向きの方が、多少楽でしょう</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>……脚が、攣ってしまいそうですわ……これは酷うございます</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>……朝ですわね。……脚が、少し強張っておりますわ</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>……朝ですわね。……脚が、少し強張っておりますわ。それに、まだ、眠気が残っておりますわ</t>
         </is>
       </c>
     </row>
@@ -3404,12 +5117,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>こちらを、下にお敷きくださいませ</t>
+          <t>……この程度でしたら、問題ございませんわ</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>……何か、下に敷けば、少しは和らぐでしょう</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>……凍えて死んでしまいそうですわ……このような冷たさ、耐えられません</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>……朝ですわね。……体が、まだ冷えておりますわ</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>……朝ですわね。……体が、まだ冷えておりますわ。それに、まだ、眠気が残っておりますわ</t>
         </is>
       </c>
     </row>
@@ -3429,12 +5157,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>わたしが、払っておきますわ</t>
+          <t>……この程度でしたら、問題ございませんわ</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>……払えば、大丈夫でしょう</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>……気持ちが悪うございますわ……とても、眠れそうにありません</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>……朝ですわね。……髪を、確認いたしませんと</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>……朝ですわね。……髪を、確認いたしませんと。それに、まだ、眠気が残っておりますわ</t>
         </is>
       </c>
     </row>
@@ -3454,12 +5197,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>……大丈夫ですか。こちらの布を、お使いくださいませ</t>
+          <t>……この程度でしたら、問題ございませんわ</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>……口元を、覆えば、少しは和らぐでしょう</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>……くしゃみが、止まりませんわ……これは、なかなか辛うございます</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>……朝ですわね。……くしゃみ、落ち着きましたわ</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>……朝ですわね。……くしゃみ、落ち着きましたわ。それに、まだ、眠気が残っておりますわ</t>
         </is>
       </c>
     </row>
@@ -3479,12 +5237,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>大丈夫ですわ。……わたしが、そばにおりますから</t>
+          <t>……気のせいでしたら、問題ございませんわ</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>……近くに、いれば、大丈夫でしょう</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>……本気で、恐ろしゅうございますわ……これは……</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>……朝ですわね。……昨夜の声、もう聞こえませんわ</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>……朝ですわね。……昨夜の声、もう聞こえませんわ。それに、まだ、眠気が残っておりますわ</t>
         </is>
       </c>
     </row>
@@ -3504,12 +5277,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>気になさらず。……わたしが、確認いたしますわ</t>
+          <t>……この程度でしたら、問題ございませんわ</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>……気にしなければ、大丈夫でしょう</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>……鳥肌が立ってしまいますわ……これは、眠れそうにありません</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>……朝ですわね。……虫は、もういないようですわ</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>……朝ですわね。……虫は、もういないようですわ。それに、まだ、眠気が残っておりますわ</t>
         </is>
       </c>
     </row>
@@ -3529,12 +5317,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>気のせいであれば、良いのですけれど……用心いたしましょう</t>
+          <t>……気のせいでしたら、問題ございませんわ</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>……気を、つければ、大丈夫でしょう</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>……生きた心地が、いたしませんわ……これは、恐ろしゅうございます</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>……朝ですわね。……あの気配、もう感じませんわ</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>……朝ですわね。……あの気配、もう感じませんわ。それに、まだ、眠気が残っておりますわ</t>
         </is>
       </c>
     </row>
@@ -3554,12 +5357,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>おそらく、建物が軋む音ですわ。……大丈夫でしょう</t>
+          <t>……この程度でしたら、問題ございませんわ</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>……建物の音、でしょう。大丈夫だと思いますわ</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>……気になって、とても眠れそうにありませんわ</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>……朝ですわね。……あの音、止まっておりますわ</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>……朝ですわね。……あの音、止まっておりますわ。それに、まだ、眠気が残っておりますわ</t>
         </is>
       </c>
     </row>
@@ -3579,12 +5397,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>久しぶりに、自分の姿を見ましたわ。……少々、驚きますわね</t>
+          <t>……珍しいだけでしたら、問題ございませんわ</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>……気にしなければ、大丈夫でしょう</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>……なんとも、不気味ですわ……とても、眠れそうにありません</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>……朝ですわね。……もう一度、鏡を、見てみましょうか</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>……朝ですわね。……もう一度、鏡を、見てみましょうか。それに、まだ、眠気が残っておりますわ</t>
         </is>
       </c>
     </row>
@@ -3599,17 +5432,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>……見張りの順番、決めなければなりませんわね</t>
+          <t>……息を潜めていれば、きっと大丈夫ですわ</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>その順番で、問題ございませんわ</t>
+          <t>……交代で務めましょう。わたしが、最初にいたしますわ</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>……朝ですわね。……見張り、無事に終えられましたわ</t>
+          <t>……順番を、決めておいた方がよろしいですわね</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>……正直、見張りは、あまり気が進みませんわ</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>……朝ですわね。……見張り、問題なく務まりましたわ</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>……朝ですわね。……あまり、眠れませんでしたわ</t>
         </is>
       </c>
     </row>
@@ -3624,17 +5472,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>……皆様に、平等に、分けなければなりませんわね</t>
+          <t>……何を、いただきましょうかしら</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>わたしの分は、少なくても構いませんわ</t>
+          <t>……この程度で、問題ございませんわ</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>……均等に、分ければ、大丈夫でしょう</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>……このように少量では……とても、足りませんわ</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>……朝ですわね。……皆様、足りましたでしょうか</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>……朝ですわね。……皆様、足りましたでしょうか。それに、まだ、眠気が残っておりますわ</t>
         </is>
       </c>
     </row>
@@ -3649,17 +5512,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>……声を、抑えなければなりませんわね</t>
+          <t>……物音を、立てないよう、気をつけませんと</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>承知いたしましたわ。……気をつけます</t>
+          <t>……この程度でしたら、問題ございませんわ</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>……気を、つければ、大丈夫でしょう</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>……ずっと、小声とは……息が詰まりそうですわ</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>……朝ですわね。……もう、声を抑えなくてよろしいのですね</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>……朝ですわね。……もう、声を抑えなくてよろしいのですね。それに、まだ、眠気が残っておりますわ</t>
         </is>
       </c>
     </row>
@@ -3674,17 +5552,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>……平らな場所が、狭うございますわね……どういたしましょう</t>
+          <t>……寒うございますわね……どういたしましょう</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>……わたくしは、端で構いませんわ</t>
+          <t>……この程度の寒さでしたら、問題ございませんわ</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>……くっつけば、暖かいと思いますわ</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>……凍えてしまいそうですわ……これでは、眠れません</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>……朝ですわね。……昨夜は、あたたかく過ごせましたわ</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>……朝ですわね。……昨夜は、あたたかく過ごせましたわ。それに、まだ、眠気が残っておりますわ</t>
         </is>
       </c>
     </row>
@@ -3704,12 +5597,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>……出来すぎていて、少々、不安になりますわね</t>
+          <t>……なかなか、綺麗な部屋ですわね</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>……綺麗な部屋で、幸運でしたわ</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>……出来すぎておりますわ……何か、裏があるとしか思えません</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>……朝ですわね。……結局、何事もありませんでしたわね</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>……朝ですわね。……結局、何事もありませんでしたわね。それに、まだ、眠気が残っておりますわ</t>
         </is>
       </c>
     </row>
@@ -3724,14 +5632,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3752,12 +5663,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>②反応</t>
+          <t>②A 友好度高</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>③朝</t>
+          <t>②B 付き合い薄い</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>②C 悪態</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>③A 疲れなし</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>③B 疲れ残り</t>
         </is>
       </c>
     </row>
@@ -3777,12 +5703,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>こっちの隅、大丈夫そうですよ</t>
+          <t>これくらいなら、大丈夫だと思いますよ</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>場所を変えれば、大丈夫だと思います</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>こんなに濡れた場所で……さすがに、辛いです……</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>朝ですね……昨日は結局、あまり眠れませんでした</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>朝ですね……昨日は結局、あまり眠れませんでした。あと、少し眠くて……</t>
         </is>
       </c>
     </row>
@@ -3802,12 +5743,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>これ、隙間に詰めてみますね</t>
+          <t>この程度なら、大丈夫だと思いますよ</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>隙間を塞げば、大丈夫だと思います</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>凍えそうです……さすがに、これは辛いです……</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>朝ですね……昨日は、少し寒かったです</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>朝ですね……昨日は、少し寒かったです。あと、少し眠くて……</t>
         </is>
       </c>
     </row>
@@ -3827,12 +5783,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>何か下に敷いたら、少し楽になるかもしれません</t>
+          <t>この程度なら、大丈夫だと思いますよ</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>壁側の方が、安定すると思います</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>転がり落ちてしまいそうです……これは、危ないです……</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>朝ですね……昨日は、少し転がってしまいました</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>朝ですね……昨日は、少し転がってしまいました。あと、少し眠くて……</t>
         </is>
       </c>
     </row>
@@ -3852,12 +5823,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>手、繋いでおきましょうか。はぐれないように</t>
+          <t>この程度なら、大丈夫だと思いますよ</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>声をかけあえば、大丈夫だと思います</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>何も見えません……これは、さすがに怖いです……</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>朝ですね……明るくなって、ほっとしました</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>朝ですね……明るくなって、ほっとしました。あと、少し眠くて……</t>
         </is>
       </c>
     </row>
@@ -3877,12 +5863,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>こっちの方が、少し匂い薄いかもしれません</t>
+          <t>ちょっと匂いますけど、大丈夫だと思いますよ</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>離れた場所に移れば、大丈夫だと思います</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>こんなに匂う場所で一晩なんて……さすがに、辛いです……</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>朝ですね……匂い、少しずつ慣れてきました</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>朝ですね……匂い、少しずつ慣れてきました。あと、少し眠くて……</t>
         </is>
       </c>
     </row>
@@ -3902,12 +5903,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>一緒にどかしましょうか</t>
+          <t>この程度なら、大丈夫だと思いますよ</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>どければ、大丈夫だと思います</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>背中が、折れそうです……これは、さすがに痛いです……</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>朝ですね……背中、少し痛いです</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>朝ですね……背中、少し痛いです。あと、少し眠くて……</t>
         </is>
       </c>
     </row>
@@ -3927,12 +5943,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>この程度なら、大丈夫だと思いますよ</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>横向きだと、少し楽かもしれません</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>脚が、攣ってしまいそうです……これは、さすがに辛いです……</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>朝ですね……脚、少し縮こまってます</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>朝ですね……脚、少し縮こまってます。あと、少し眠くて……</t>
         </is>
       </c>
     </row>
@@ -3952,12 +5983,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>これ、下に敷きましょうか</t>
+          <t>この程度なら、大丈夫だと思いますよ</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>何か敷けば、少し楽になると思います</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>凍えてしまいそうです……さすがに、これは辛いです……</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>朝ですね……体、少し冷えています</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>朝ですね……体、少し冷えています。あと、少し眠くて……</t>
         </is>
       </c>
     </row>
@@ -3977,12 +6023,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>払っておきますね、大丈夫ですよ</t>
+          <t>この程度なら、大丈夫だと思いますよ</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>払えば、大丈夫だと思います</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>うっ……これは、さすがに気持ち悪くて眠れないかもしれません</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>朝ですね……髪、確認しておきましょうか</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>朝ですね……髪、確認しておきましょうか。あと、少し眠くて……</t>
         </is>
       </c>
     </row>
@@ -4002,12 +6063,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>大丈夫ですか? これ、口に当ててください</t>
+          <t>この程度なら、大丈夫だと思いますよ</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>口を覆えば、少し楽になると思います</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>くしゃみが、止まりません……これは、さすがに辛いです……</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>朝ですね……くしゃみ、少し落ち着きました</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>朝ですね……くしゃみ、少し落ち着きました。あと、少し眠くて……</t>
         </is>
       </c>
     </row>
@@ -4027,12 +6103,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>大丈夫ですよ、みんな一緒にいますから</t>
+          <t>気のせいだと思います、大丈夫ですよ</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>近くにいれば、大丈夫だと思います</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>本気で、怖いです……これは、さすがに……</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>朝ですね……昨日の声、もう聞こえません</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>朝ですね……昨日の声、もう聞こえません。あと、少し眠くて……</t>
         </is>
       </c>
     </row>
@@ -4052,12 +6143,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>大丈夫ですよ、わたし、虫平気なので見てみますね</t>
+          <t>この程度なら、大丈夫だと思いますよ</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>気にしなければ、大丈夫だと思います</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>鳥肌が……これは、さすがに眠れないかもしれません</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>朝ですね……虫、もういないみたいです</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>朝ですね……虫、もういないみたいです。あと、少し眠くて……</t>
         </is>
       </c>
     </row>
@@ -4077,12 +6183,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>気のせいだといいですね……でも、気をつけましょう</t>
+          <t>気のせいだと思います、大丈夫ですよ</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>気をつければ、大丈夫だと思います</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>生きた心地がしません……これは、さすがに……</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>朝ですね……あの気配、もう感じません</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>朝ですね……あの気配、もう感じません。あと、少し眠くて……</t>
         </is>
       </c>
     </row>
@@ -4102,12 +6223,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>きっと、建物の音だと思います。大丈夫ですよ</t>
+          <t>この程度なら、大丈夫だと思いますよ</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>建物の音だと思います、大丈夫ですよ</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>気になって、眠れません……これは、さすがに……</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>朝ですね……あの音、止まっています</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>朝ですね……あの音、止まっています。あと、少し眠くて……</t>
         </is>
       </c>
     </row>
@@ -4127,12 +6263,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>久しぶりに、自分の顔見ました……なんだか不思議です</t>
+          <t>珍しいだけだと思いますよ、大丈夫です</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>気にしなければ、大丈夫だと思います</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>なんだか、不気味です……これは、さすがに眠れないかも……</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>朝ですね……また鏡、見てみましょうか</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>朝ですね……また鏡、見てみましょうか。あと、少し眠くて……</t>
         </is>
       </c>
     </row>
@@ -4147,17 +6298,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>見張りの順番、決めましょうか。……わたし、先でも大丈夫ですよ</t>
+          <t>静かにしていれば、大丈夫だと思います</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>その順番で大丈夫ですよ、頑張りましょう</t>
+          <t>交代でやりましょうか。わたし、先でも大丈夫ですよ</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>朝ですね……見張り、無事に終わってよかったです</t>
+          <t>順番、決めておきましょうか……</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>見張り、少し苦手かもしれません……</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>朝ですね……見張り、無事にこなせました</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>朝ですね……あまり眠れなくて、少し眠いです</t>
         </is>
       </c>
     </row>
@@ -4172,17 +6338,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>みんなの分、ちゃんと分けますね……ちょっと難しいですけど</t>
+          <t>何、食べましょうか</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>わたしは大丈夫ですよ、みんな先にどうぞ</t>
+          <t>これくらいで、大丈夫だと思いますよ</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>均等に分ければ、大丈夫だと思います</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>こんなに少ないと……お腹、すいてしまいます……</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>朝ですね……みんな、ちゃんと食べられたでしょうか</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>朝ですね……みんな、ちゃんと食べられたでしょうか。あと、少し眠くて……</t>
         </is>
       </c>
     </row>
@@ -4197,17 +6378,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>静かに、お話しましょうか</t>
+          <t>物音、気をつけましょうか</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>はい、気をつけますね</t>
+          <t>この程度なら、大丈夫だと思いますよ</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>気をつければ、大丈夫だと思います</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>ずっと小声だと……なんだか、息が詰まります……</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>朝ですね……もう、普通の声で大丈夫ですね</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>朝ですね……もう、普通の声で大丈夫ですね。あと、少し眠くて……</t>
         </is>
       </c>
     </row>
@@ -4222,17 +6418,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>平らな場所、狭いですね……くっついた方がいいかもしれません</t>
+          <t>寒いですね……何か、暖まる方法探しましょうか</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>わたしは、隅の方で大丈夫ですよ</t>
+          <t>この程度なら、大丈夫だと思いますよ</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>くっつけば、暖かいと思います</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>凍えそうです……これは、さすがに眠れません……</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>朝ですね……昨日は、あたたかく眠れました</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>朝ですね……昨日は、あたたかく眠れました。あと、少し眠くて……</t>
         </is>
       </c>
     </row>
@@ -4252,12 +6463,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>嬉しいですけど、念のため、注意はしておきましょうか</t>
+          <t>ちょっと綺麗な部屋ですね</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>綺麗な部屋で、よかったと思います</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>出来すぎです……何か、あるかもしれません……</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>朝ですね……結局、何もなくてよかったです</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>朝ですね……結局、何もなくてよかったです。あと、少し眠くて……</t>
         </is>
       </c>
     </row>
@@ -4272,14 +6498,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4300,12 +6529,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>②反応</t>
+          <t>②A 友好度高</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>③朝</t>
+          <t>②B 付き合い薄い</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>②C 悪態</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>③A 疲れなし</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>③B 疲れ残り</t>
         </is>
       </c>
     </row>
@@ -4325,12 +6569,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>……こっち、来て……大丈夫、だから……</t>
+          <t>……この、くらいなら……平気……</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>……場所……変えれば、大丈夫……</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>……こんな、水浸しの場所で……眠れない……無理……</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>……朝……昨日の、雨の音……まだ、耳に、残ってる……</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>……朝……昨日の、雨の音……まだ、耳に、残ってる……。まだ、眠い……疲れ、取れて、ない……</t>
         </is>
       </c>
     </row>
@@ -4350,12 +6609,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>……これ、使って……少しは、マシに、なる、かも……</t>
+          <t>……この、くらいなら……平気……</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>……隙間、塞げば……大丈夫……</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>……凍える……こんなの、耐えられ、ない……</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>……朝……寒くて、あんまり、眠れなかった……</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>……朝……寒くて、あんまり、眠れなかった……。まだ、眠い……疲れ、取れて、ない……</t>
         </is>
       </c>
     </row>
@@ -4375,12 +6649,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>……壁、側……そっちの方が、いい、かも……</t>
+          <t>……この、くらいなら……平気……</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>……壁側、なら……安定……する、かも……</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>……転がり、落ちる……怖い……無理……</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>……朝……何回か、転がった、気が、する……</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>……朝……何回か、転がった、気が、する……。まだ、眠い……疲れ、取れて、ない……</t>
         </is>
       </c>
     </row>
@@ -4400,12 +6689,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>……そば、いる、から……大丈夫……</t>
+          <t>……この、くらいなら……平気……</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>……声、かけあえば……大丈夫……</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>……なにも、見えない……怖い……無理……</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>……朝……明るい……よかった……</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>……朝……明るい……よかった……。まだ、眠い……疲れ、取れて、ない……</t>
         </is>
       </c>
     </row>
@@ -4425,12 +6729,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>……こっち……少し、マシ、かも……</t>
+          <t>……ちょっと、匂う、けど……平気……</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>……離れた場所……行けば……大丈夫……</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>……こんな、臭い場所で……無理……耐えられ、ない……</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>……朝……匂い……まだ、少し、残ってる、気が……</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>……朝……匂い……まだ、少し、残ってる、気が……。まだ、眠い……疲れ、取れて、ない……</t>
         </is>
       </c>
     </row>
@@ -4450,12 +6769,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>……どかす、の、手伝う……</t>
+          <t>……この、くらいなら……平気……</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>……どければ……大丈夫……</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>……背中……折れそう……痛い……無理……</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>……朝……背中……まだ、痛い……</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>……朝……背中……まだ、痛い……。まだ、眠い……疲れ、取れて、ない……</t>
         </is>
       </c>
     </row>
@@ -4475,12 +6809,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>……横、向いたら……ちょっと、楽……かも……</t>
+          <t>……この、くらいなら……平気……</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>……横向き、なら……ちょっと、楽……</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>……脚……攣りそう……動け、ない……</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>……朝……脚……固まって、る……</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>……朝……脚……固まって、る……。まだ、眠い……疲れ、取れて、ない……</t>
         </is>
       </c>
     </row>
@@ -4500,12 +6849,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>……これ、敷いて……少し、あったかい、かも……</t>
+          <t>……この、くらいなら……平気……</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>……何か、敷けば……少し、楽……</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>……凍える……こんなの、無理……眠れ、ない……</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>……朝……まだ、冷たい……</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>……朝……まだ、冷たい……。まだ、眠い……疲れ、取れて、ない……</t>
         </is>
       </c>
     </row>
@@ -4525,12 +6889,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>……払う、の、手伝う……</t>
+          <t>……この、くらいなら……平気……</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>……払えば……大丈夫……</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>……気持ち、悪い……眠れ、ない……無理……</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>……朝……髪……蜘蛛の巣、ついてない、かな……</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>……朝……髪……蜘蛛の巣、ついてない、かな……。まだ、眠い……疲れ、取れて、ない……</t>
         </is>
       </c>
     </row>
@@ -4550,12 +6929,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>……大丈夫……？ ……これ、使って……</t>
+          <t>……この、くらいなら……平気……</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>……口、覆えば……少し、楽……</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>……くしゃみ……止まらない……辛い……</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>……朝……くしゃみ……少し、落ち着いた……</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>……朝……くしゃみ……少し、落ち着いた……。まだ、眠い……疲れ、取れて、ない……</t>
         </is>
       </c>
     </row>
@@ -4575,12 +6969,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>……大丈夫……そば、いる……</t>
+          <t>……気のせい……平気……</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>……近く、いれば……大丈夫……</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>……っ、本気で、怖い……これ……</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>……朝……あの声……もう、聞こえ、ない……</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>……朝……あの声……もう、聞こえ、ない……。まだ、眠い……疲れ、取れて、ない……</t>
         </is>
       </c>
     </row>
@@ -4600,12 +7009,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>……気に、しない……方が……</t>
+          <t>……この、くらいなら……平気……</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>……気に、しなければ……大丈夫……</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>……鳥肌……眠れ、ない……無理……</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>……朝……虫……もう、いない、みたい……</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>……朝……虫……もう、いない、みたい……。まだ、眠い……疲れ、取れて、ない……</t>
         </is>
       </c>
     </row>
@@ -4625,12 +7049,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>……気を、つけよう……</t>
+          <t>……気のせい……平気……</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>……気を、つければ……大丈夫……</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>……っ、生きた心地、しない……これ……</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>……朝……あの気配……もう、しない……</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>……朝……あの気配……もう、しない……。まだ、眠い……疲れ、取れて、ない……</t>
         </is>
       </c>
     </row>
@@ -4650,12 +7089,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>……たぶん、大丈夫……音、だけ……</t>
+          <t>……この、くらいなら……平気……</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>……建物の、音……大丈夫、だと、思う……</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>……気になって……眠れ、ない……</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>……朝……あの音……止まって、る……</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>……朝……あの音……止まって、る……。まだ、眠い……疲れ、取れて、ない……</t>
         </is>
       </c>
     </row>
@@ -4675,12 +7129,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>……久しぶりに、自分の、顔……見た……</t>
+          <t>……珍しい、だけ……平気……</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>……気に、しなければ……大丈夫……</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>……不気味……眠れ、ない……怖い……</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>……朝……鏡……また、見て、みようか、な……</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>……朝……鏡……また、見て、みようか、な……。まだ、眠い……疲れ、取れて、ない……</t>
         </is>
       </c>
     </row>
@@ -4695,17 +7164,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>……見張り……誰から、する……？</t>
+          <t>……隠れて、れば……大丈夫、かな……</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>……その、順番で……大丈夫……</t>
+          <t>……交代、しよう……わたし、最初……やる……</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>……朝……見張り……終わった……</t>
+          <t>……順番……決めた方、いい……かな……</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>……見張り……あんまり、得意じゃ、ない……</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>……朝……見張り……ちゃんと、できた……</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>……朝……あんまり、眠れなかった……眠い……</t>
         </is>
       </c>
     </row>
@@ -4720,17 +7204,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>……分ける、の……ちゃんと、できる、かな……</t>
+          <t>……何、食べよう、かな……</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>……わたし、少なくて、いい……から……</t>
+          <t>……これくらい、なら……平気……</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>……均等に、分ければ……大丈夫……</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>……少ない……お腹、すく……辛い……</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>……朝……みんな、ちゃんと……食べられた、かな……</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>……朝……みんな、ちゃんと……食べられた、かな……。まだ、眠い……疲れ、取れて、ない……</t>
         </is>
       </c>
     </row>
@@ -4745,17 +7244,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>……小さい、声で……話す……</t>
+          <t>……物音……気を、つけないと……</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>……うん……気を、つける……</t>
+          <t>……この、くらいなら……平気……</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>……気を、つければ……大丈夫……</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>……ずっと、小声……苦しい……</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>……朝……もう、大きい、声……出せる……</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>……朝……もう、大きい、声……出せる……。まだ、眠い……疲れ、取れて、ない……</t>
         </is>
       </c>
     </row>
@@ -4770,17 +7284,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>……せまい……くっつく、しか……</t>
+          <t>……寒い……どう、しよう……</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>……くっついても……いいですか……？</t>
+          <t>……この、くらいなら……平気……</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>……くっつけば……暖かい、かも……</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>……凍える……眠れ、ない……無理……</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>……朝……あったかかった……ちょっと、嬉しかった、かも……</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>……朝……あったかかった……ちょっと、嬉しかった、かも……。まだ、眠い……疲れ、取れて、ない……</t>
         </is>
       </c>
     </row>
@@ -4800,12 +7329,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>……嬉しい……けど、ちょっと、怖い……かも……</t>
+          <t>……ちょっと、綺麗……程度……</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>……綺麗な、部屋で……よかった……</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>……出来すぎ……怖い……何か、ある……</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>……朝……何も、なかった……よかった……</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>……朝……何も、なかった……よかった……。まだ、眠い……疲れ、取れて、ない……</t>
         </is>
       </c>
     </row>
@@ -4820,14 +7364,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4848,12 +7395,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>②反応</t>
+          <t>②A 友好度高</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>③朝</t>
+          <t>②B 付き合い薄い</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>②C 悪態</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>③A 疲れなし</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>③B 疲れ残り</t>
         </is>
       </c>
     </row>
@@ -4873,12 +7435,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>こっちおいでよ! 一緒に避難しよ</t>
+          <t>これくらいなら平気平気!</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>場所変えれば大丈夫だよ</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>えっ、こんなびしょびしょの場所で寝るの!? 無理じゃない!?</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>朝だ! 昨日の雨漏り、なんとか凌げたね</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 昨日の雨漏り、なんとか凌げたね。あと、なんか眠いかも</t>
         </is>
       </c>
     </row>
@@ -4898,12 +7475,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>これ使お! 隙間、塞いじゃおう</t>
+          <t>これくらいの風、平気平気!</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>隙間塞げば大丈夫だよ</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これ凍えちゃうよ!? 無理じゃない!?</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>朝だ! 昨日、ちょっと寒かったね</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 昨日、ちょっと寒かったね。あと、なんか眠いかも</t>
         </is>
       </c>
     </row>
@@ -4923,12 +7515,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>壁側行こ! そっちの方が安全そうだよ</t>
+          <t>この程度の傾き、余裕だよ!</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>壁側なら安定すると思う</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これ転がり落ちちゃわない!? 危なくない!?</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>朝だ! 昨日、結構転がったね、わたし</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 昨日、結構転がったね、わたし。あと、なんか眠いかも</t>
         </is>
       </c>
     </row>
@@ -4948,12 +7555,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>みんなここにいるよー! 声出してね</t>
+          <t>この程度の暗さ、平気平気!</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>声かけあえば大丈夫だよ</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>えっ、本当に何も見えない!? これ怖くない!?</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>朝だ! 明るくなって、ちょっと安心したよ</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 明るくなって、ちょっと安心したよ。あと、なんか眠いかも</t>
         </is>
       </c>
     </row>
@@ -4973,12 +7595,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>こっちおいでよ、少し離れよう</t>
+          <t>ちょっと匂うけど平気平気!</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>離れた場所に移れば大丈夫だよ</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>えっ、こんな臭い場所で一晩なの!? 無理じゃない!?</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>朝だ! 匂い、だいぶ慣れたかも</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 匂い、だいぶ慣れたかも。あと、なんか眠いかも</t>
         </is>
       </c>
     </row>
@@ -4998,12 +7635,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>どかそっか、一緒に!</t>
+          <t>この程度の石、平気平気!</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>どければ大丈夫だよ</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これ背骨折れちゃいそうなんだけど!? 痛すぎない!?</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>朝だ! 背中、ちょっと痛いかも</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 背中、ちょっと痛いかも。あと、なんか眠いかも</t>
         </is>
       </c>
     </row>
@@ -5023,12 +7675,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>横向きにしてみたら? ちょっと楽になるかも</t>
+          <t>この程度の狭さ、平気平気!</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>横向きにしたら少し楽になるかも</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これ脚攣っちゃいそうなんだけど!? やばくない!?</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>朝だ! 脚、ちょっと固まっちゃった</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 脚、ちょっと固まっちゃった。あと、なんか眠いかも</t>
         </is>
       </c>
     </row>
@@ -5048,12 +7715,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>これ使お! 下に敷こう</t>
+          <t>この程度の冷たさ、平気平気!</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>何か敷けば少しマシになるよ</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これ凍死しちゃいそうなんだけど!? 無理じゃない!?</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>朝だ! 体、まだちょっと冷えてるかも</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 体、まだちょっと冷えてるかも。あと、なんか眠いかも</t>
         </is>
       </c>
     </row>
@@ -5073,12 +7755,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>払っとくね! まかせて</t>
+          <t>この程度の蜘蛛の巣、平気平気!</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>払えば大丈夫だよ</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>うわぁ、これ気持ち悪すぎて眠れないよ!?</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>朝だ! 髪、蜘蛛の巣ついてないか見てみよ</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 髪、蜘蛛の巣ついてないか見てみよ。あと、なんか眠いかも</t>
         </is>
       </c>
     </row>
@@ -5098,12 +7795,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>大丈夫? これ使って!</t>
+          <t>この程度の埃、平気平気!</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>口覆えば少しマシになるよ</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>えっ、くしゃみ止まらないんだけど!? キツくない!?</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>朝だ! くしゃみ、だいぶ収まったよ</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! くしゃみ、だいぶ収まったよ。あと、なんか眠いかも</t>
         </is>
       </c>
     </row>
@@ -5123,12 +7835,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>大丈夫だよ、みんなここにいるから!</t>
+          <t>気のせいだよ、平気平気!</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>近くにいれば大丈夫だよ</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>えっ、今の本気で怖いんだけど!?</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>朝だ! 昨日の声、もう聞こえないね</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 昨日の声、もう聞こえないね。あと、なんか眠いかも</t>
         </is>
       </c>
     </row>
@@ -5148,12 +7875,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>気にしない気にしない! 大丈夫だよ</t>
+          <t>この程度の虫、平気平気!</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>気にしなければ大丈夫だよ</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>うわぁ、鳥肌立って眠れないんだけど!?</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>朝だ! 昨日の虫、もういないね</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 昨日の虫、もういないね。あと、なんか眠いかも</t>
         </is>
       </c>
     </row>
@@ -5173,12 +7915,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>気のせいだといいね! でも一応気をつけよっか</t>
+          <t>気のせいだよ、平気平気!</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>気をつければ大丈夫だよ</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これ生きた心地しないんだけど!?</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>朝だ! 昨日の気配、もう感じないね</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 昨日の気配、もう感じないね。あと、なんか眠いかも</t>
         </is>
       </c>
     </row>
@@ -5198,12 +7955,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>たぶん建物の音だよ! 大丈夫大丈夫</t>
+          <t>この程度の音、平気平気!</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>建物の音だと思うよ、大丈夫</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これ気になって眠れないんだけど!?</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>朝だ! 昨日の音、止まってるね</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 昨日の音、止まってるね。あと、なんか眠いかも</t>
         </is>
       </c>
     </row>
@@ -5223,12 +7995,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>久しぶりに自分の顔見たね! なんか変な感じ</t>
+          <t>珍しいだけだよ、平気平気!</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>気にしなければ大丈夫だよ</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これなんか不気味すぎて眠れないんだけど!?</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>朝だ! また鏡見てみよっか</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! また鏡見てみよっか。あと、なんか眠いかも</t>
         </is>
       </c>
     </row>
@@ -5243,17 +8030,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>見張りの順番決めよっか! じゃんけんする?</t>
+          <t>静かにしてれば、大丈夫かな</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>その順番でいこっか! みんな頑張ろう</t>
+          <t>交代でやろっか! わたし最初やるよ</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>朝だ! 見張り、ちゃんと終えられたね</t>
+          <t>順番、決めておこっか</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>見張りかぁ……正直、ちょっと眠いんだよね</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 見張り、ばっちりだったよ</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>朝だ……眠い、あんまり寝れなかったかも</t>
         </is>
       </c>
     </row>
@@ -5268,17 +8070,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>みんなの分、ちゃんと分けよっか! 難しいね、これ</t>
+          <t>何食べようかな〜</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>わたしは少なくていいよ! みんな食べて</t>
+          <t>これくらいで平気平気!</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>均等に分ければ大丈夫だよ</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これだけ!? さすがに少なすぎない!?</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>朝だ! みんな、ちゃんと食べられたかな</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! みんな、ちゃんと食べられたかな。あと、なんか眠いかも</t>
         </is>
       </c>
     </row>
@@ -5293,17 +8110,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>静かにお話しよっか、ヒソヒソね</t>
+          <t>物音、気をつけないとだね</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>了解! 静かにするね</t>
+          <t>この程度、平気平気!</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>気をつければ大丈夫だよ</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>えっ、ずっと小声なのキツくない!? 息詰まりそう!</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>朝だ! もう普通に喋れるね</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! もう普通に喋れるね。あと、なんか眠いかも</t>
         </is>
       </c>
     </row>
@@ -5318,17 +8150,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>平らな場所狭いね! くっついちゃう?</t>
+          <t>寒いね〜……何か暖まる方法ないかな</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>くっついちゃおうよ! あったかいし</t>
+          <t>この程度の寒さ、平気平気!</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>くっつけば暖かいと思うよ</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これ凍えて眠れないんだけど!?</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>朝だ! 昨日、あったかくて意外とよく眠れたよ</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 昨日、あったかくて意外とよく眠れたよ。あと、なんか眠いかも</t>
         </is>
       </c>
     </row>
@@ -5348,12 +8195,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>ラッキーだね! でも一応、気をつけとこっか</t>
+          <t>ちょっと綺麗な部屋だね</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>綺麗な部屋でよかったよ</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>えっ、これ出来すぎてない!? 絶対なんかあるよ!</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>朝だ! 結局何もなかったね、よかった</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>朝だ! 結局何もなかったね、よかった。あと、なんか眠いかも</t>
         </is>
       </c>
     </row>
@@ -5368,14 +8230,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5396,12 +8261,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>②反応</t>
+          <t>②A 友好度高</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>③朝</t>
+          <t>②B 付き合い薄い</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>②C 悪態</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>③A 疲れなし</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>③B 疲れ残り</t>
         </is>
       </c>
     </row>
@@ -5421,12 +8301,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>こっち来い、まだ乾いとるで</t>
+          <t>これくらいの雨漏り、屁でもないわ</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>場所変えたらええだけやろ</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? こんなびしょびしょの場所で寝るとか、正気かいな</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>朝きたなぁ……昨日の雨漏り、結構うるさかったわ</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>朝きたなぁ……昨日の雨漏り、結構うるさかったわ。あと、なんか体がだるいわ</t>
         </is>
       </c>
     </row>
@@ -5446,12 +8341,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>これ詰めとこか、少しはマシになるやろ</t>
+          <t>この程度の風、屁でもないわ</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>隙間塞いだらええだけやろ</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? 凍え死ぬくらい寒いんやけど、なんとかしてぇな</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>朝やな……昨日の風、結構冷えたわ</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>朝やな……昨日の風、結構冷えたわ。あと、なんか体がだるいわ</t>
         </is>
       </c>
     </row>
@@ -5471,12 +8381,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>壁にくっついとったら転がらんやろ</t>
+          <t>この程度、屁でもないわ</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>壁側やったら安定するやろ</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? これ寝てる間に転げ落ちるやつやん、危なすぎるわ</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>朝やな……昨日、何回か転がった気がするわ</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>朝やな……昨日、何回か転がった気がするわ。あと、なんか体がだるいわ</t>
         </is>
       </c>
     </row>
@@ -5496,12 +8421,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>声かけあお、はぐれたらあかんし</t>
+          <t>この程度、屁でもないわ</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>声かけあってたら平気やろ</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? マジで真っ暗やん、これ怖すぎるわ</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>朝やな……明るいと、やっぱ安心するわ</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>朝やな……明るいと、やっぱ安心するわ。あと、なんか体がだるいわ</t>
         </is>
       </c>
     </row>
@@ -5521,12 +8461,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>こっち来い、多少マシやで</t>
+          <t>ちょっと匂うくらい、屁でもないわ</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>離れたら大丈夫やろ</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? こんな臭い場所で一晩過ごすとか、正気かいな</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>朝やな……あの匂い、結局慣れたような慣れてないような</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>朝やな……あの匂い、結局慣れたような慣れてないような。あと、なんか体がだるいわ</t>
         </is>
       </c>
     </row>
@@ -5546,12 +8501,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>どかしたるわ、待っとき</t>
+          <t>この程度、屁でもないわ</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>どけたら大丈夫やろ</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? 背骨イカれそうなくらい痛いんやけど、マジか</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>朝やな……背中痛いわ、あの石のせいやな</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>朝やな……背中痛いわ、あの石のせいやな。あと、なんか体がだるいわ</t>
         </is>
       </c>
     </row>
@@ -5571,12 +8541,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>横向いたらちょっとはマシになるんちゃう</t>
+          <t>この程度、屁でもないわ</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>横向いたら多少マシになるやろ</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? 脚攣って動けんくなりそうやわ、これ</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>朝やな……脚、固まってもうたわ</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>朝やな……脚、固まってもうたわ。あと、なんか体がだるいわ</t>
         </is>
       </c>
     </row>
@@ -5596,12 +8581,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>これ敷いとき、多少はマシになるで</t>
+          <t>この程度、屁でもないわ</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>何か敷いたらマシになるやろ</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? 芯まで凍えるくらい冷たいんやけど、なんとかしてぇな</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>朝やな……体、まだ冷えとるわ</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>朝やな……体、まだ冷えとるわ。あと、なんか体がだるいわ</t>
         </is>
       </c>
     </row>
@@ -5621,12 +8621,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>払っといたるわ、待っとき</t>
+          <t>この程度、屁でもないわ</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>払ったら大丈夫やろ</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>うわ、キモすぎるわ! こんなん払っても切りないやん</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>朝やな……髪、蜘蛛の巣ついてへんか確認せな</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>朝やな……髪、蜘蛛の巣ついてへんか確認せな。あと、なんか体がだるいわ</t>
         </is>
       </c>
     </row>
@@ -5646,12 +8661,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>大丈夫か? これで口塞いどき</t>
+          <t>この程度、屁でもないわ</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>口塞いだらマシになるやろ</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>はっくしょん! くしゃみ止まらんわ、ここ埃っぽすぎるで</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>朝やな……くしゃみ、やっと収まったわ</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>朝やな……くしゃみ、やっと収まったわ。あと、なんか体がだるいわ</t>
         </is>
       </c>
     </row>
@@ -5671,12 +8701,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>大丈夫や、うちがついとるから</t>
+          <t>気のせいやろ、屁でもないわ</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>近くにおったら平気やろ</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? 今の本気でヤバかったやん、怖すぎるわ</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>朝やな……昨日の声、もう聞こえへんな</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>朝やな……昨日の声、もう聞こえへんな。あと、なんか体がだるいわ</t>
         </is>
       </c>
     </row>
@@ -5696,12 +8741,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>気にすんな、山じゃもっとおったで</t>
+          <t>この程度、屁でもないわ</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>気にせんかったら平気やろ</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>うわ、鳥肌やば! 眠れんわこれ、マジで</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>朝やな……昨日の虫、もうおらんみたいやな</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>朝やな……昨日の虫、もうおらんみたいやな。あと、なんか体がだるいわ</t>
         </is>
       </c>
     </row>
@@ -5721,12 +8781,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>気のせいならええけど、一応気張っとこ</t>
+          <t>気のせいやろ、屁でもないわ</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>気ぃつけとったら平気やろ</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? マジで見られとる気しかせんわ、無理やこれ</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>朝やな……昨日の気配、もう感じへんな</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>朝やな……昨日の気配、もう感じへんな。あと、なんか体がだるいわ</t>
         </is>
       </c>
     </row>
@@ -5746,12 +8821,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>たぶん建物のきしみやろ、心配せんでええ</t>
+          <t>この程度、屁でもないわ</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>建物の音やろ、平気やろ</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? あの音マジでうるさいんやけど、眠れんわ</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>朝やな……あの音、止まっとるわ</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>朝やな……あの音、止まっとるわ。あと、なんか体がだるいわ</t>
         </is>
       </c>
     </row>
@@ -5771,12 +8861,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>久しぶりに自分の顔見たわ……なんか変な感じやな</t>
+          <t>珍しいだけやろ、屁でもないわ</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>気にせんかったら平気やろ</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>うわ、なんか不気味すぎるわ、これ呪われとらんか</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>朝やな……もっぺん鏡見てみよか</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>朝やな……もっぺん鏡見てみよか。あと、なんか体がだるいわ</t>
         </is>
       </c>
     </row>
@@ -5791,17 +8896,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>見張り誰からするんや? うちは別にいつでもええで</t>
+          <t>じっとしとったら、まあバレへんやろ</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>その順番でええんちゃう、まあ気楽にな</t>
+          <t>交代しよか、うち最初やったるわ</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>朝やな……見張り、なんとかなったわ</t>
+          <t>順番、決めとこか</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>見張りとか、正直めんどいわ</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>朝やな……見張り、余裕やったわ</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>朝やな……見張りのせいで、あんま寝れんかったわ</t>
         </is>
       </c>
     </row>
@@ -5816,17 +8936,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>分けるん、ちょっと気ぃ遣うなぁ、これ</t>
+          <t>何食べよかなぁ</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>うちは少なめでええで、遠慮せんと</t>
+          <t>これくらいで平気やわ、余裕やん</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>均等に分けたら大丈夫やろ</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? こんだけしかないんかい、腹減りすぎるわ</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>朝やな……みんな、ちゃんと食えたかな</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>朝やな……みんな、ちゃんと食えたかな。あと、なんか体がだるいわ</t>
         </is>
       </c>
     </row>
@@ -5841,17 +8976,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>静かに喋らなあかんなぁ、これ</t>
+          <t>物音、気ぃつけとかな</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>おっけー、気ぃつけるわ</t>
+          <t>この程度、屁でもないわ</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>気ぃつけとったら平気やろ</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>はぁ、ずっとヒソヒソとか息苦しいわ、これ</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>朝やな……もう普通に喋ってええんやな</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>朝やな……もう普通に喋ってええんやな。あと、なんか体がだるいわ</t>
         </is>
       </c>
     </row>
@@ -5866,17 +9016,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>平らな場所せまいなぁ……くっつくか</t>
+          <t>さっみぃな……なんか暖まる方法ないかな</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>うちはどこでも平気やで、隅で丸まっとくわ</t>
+          <t>この程度、屁でもないわ</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>くっついたら暖かいやろ</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? 凍え死ぬくらい寒いんやけど、マジか</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>朝やな……昨日、あったかかったわ</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>朝やな……昨日、あったかかったわ。あと、なんか体がだるいわ</t>
         </is>
       </c>
     </row>
@@ -5896,12 +9061,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>ラッキーやなぁ! でも一応気ぃつけとこ</t>
+          <t>まあまあ綺麗な部屋やな</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>綺麗な部屋でラッキーやったわ</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>はぁ!? 出来すぎやろ、これ絶対裏あるで</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>朝やな……結局何もなかったわ、よかったな</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>朝やな……結局何もなかったわ、よかったな。あと、なんか体がだるいわ</t>
         </is>
       </c>
     </row>
@@ -5916,14 +9096,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5944,12 +9127,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>②反応</t>
+          <t>②A 友好度高</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>③朝</t>
+          <t>②B 付き合い薄い</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>②C 悪態</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>③A 疲れなし</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>③B 疲れ残り</t>
         </is>
       </c>
     </row>
@@ -5969,12 +9167,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>こちらの角は乾燥している。移動しろ</t>
+          <t>この程度の浸水なら、睡眠に支障はないだろう</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>場所を変えれば、問題は解消される</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>こんな環境で一晩過ごすなど、正気とは思えないな</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>夜間の水滴音、結局最後まで続いていたな……睡眠の質が低下した</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>夜間の水滴音、結局最後まで続いていたな……睡眠の質が低下した。疲労が、まだ残っているようだな</t>
         </is>
       </c>
     </row>
@@ -5994,12 +9207,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>この布で隙間を塞ぐ。応急処置としては十分だ</t>
+          <t>この程度の気流なら、体温維持に問題はないだろう</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>隙間を塞げば、問題は解消される</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>これは低体温症のリスクがあるレベルだな……深刻だ</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>体温低下を感知していたな……睡眠効率が悪かった</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>体温低下を感知していたな……睡眠効率が悪かった。疲労が、まだ残っているようだな</t>
         </is>
       </c>
     </row>
@@ -6019,12 +9247,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>壁際なら傾斜の影響を受けにくい。そちらを使え</t>
+          <t>この程度の傾斜なら、問題なく睡眠を取れるだろう</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>壁際なら、傾斜の影響を軽減できる</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>この傾斜角では、転落のリスクが無視できないな</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>夜間、複数回体位が移動していたようだな……傾斜の影響だろう</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>夜間、複数回体位が移動していたようだな……傾斜の影響だろう。疲労が、まだ残っているようだな</t>
         </is>
       </c>
     </row>
@@ -6044,12 +9287,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>定期的に声を出せ。位置確認のためだ</t>
+          <t>この程度の暗さなら、慣れれば行動できるだろう</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>声を掛け合えば、位置は把握できる</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>完全な暗黒か……視覚情報ゼロは、深刻な状況だな</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>光量が回復したな……視覚情報が使えるのはありがたい</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>光量が回復したな……視覚情報が使えるのはありがたい。疲労が、まだ残っているようだな</t>
         </is>
       </c>
     </row>
@@ -6069,12 +9327,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>換気できる位置に移動しよう。多少改善するはずだ</t>
+          <t>この程度の悪臭なら、睡眠に支障はないだろう</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>離れた位置に移動すれば、問題は解消される</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>この悪臭環境で一晩とは、衛生上も精神衛生上も問題があるな</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>嗅覚の順応が起きていたようだな……朝には気にならなくなっていた</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>嗅覚の順応が起きていたようだな……朝には気にならなくなっていた。疲労が、まだ残っているようだな</t>
         </is>
       </c>
     </row>
@@ -6094,12 +9367,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>退けろ。放置する理由がない</t>
+          <t>この程度の圧迫なら、睡眠に支障はないだろう</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>石を除去すれば、問題は解消される</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>脊椎に持続的な負荷がかかっているな……これは看過できない</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>背部に軽度の痛みが残っているな……石の影響だろう</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>背部に軽度の痛みが残っているな……石の影響だろう。疲労が、まだ残っているようだな</t>
         </is>
       </c>
     </row>
@@ -6119,12 +9407,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>横臥位を取れ。多少の緩和にはなる</t>
+          <t>この程度の空間なら、睡眠に支障はないだろう</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>横臥位なら、多少の緩和にはなる</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>この姿勢の継続は、下肢の血行不良を招く危険性があるな</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>下肢の可動域が制限されていたな……ストレッチが必要だ</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>下肢の可動域が制限されていたな……ストレッチが必要だ。疲労が、まだ残っているようだな</t>
         </is>
       </c>
     </row>
@@ -6144,12 +9447,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>この布を敷け。熱損失を軽減できる</t>
+          <t>この程度の温度なら、体温調節の範囲内だろう</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>断熱材を敷けば、熱損失を軽減できる</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>これは低体温症のリスクレベルだな……深刻な状況だ</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>体温がまだ十分回復していないな……活動を始めれば戻るだろう</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>体温がまだ十分回復していないな……活動を始めれば戻るだろう。疲労が、まだ残っているようだな</t>
         </is>
       </c>
     </row>
@@ -6169,12 +9487,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>払っておく。作業は単純だ</t>
+          <t>この程度の付着物なら、衛生上問題ないだろう</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>払えば、問題は解消される</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>この密度は異常だな……不快感が睡眠の妨げになるレベルだ</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>髪部への付着物を確認する必要があるな</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>髪部への付着物を確認する必要があるな。疲労が、まだ残っているようだな</t>
         </is>
       </c>
     </row>
@@ -6194,12 +9527,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>布で口元を覆え。粒子の吸入を防げる</t>
+          <t>この程度の粒子濃度なら、問題ないだろう</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>口元を覆えば、吸入量を軽減できる</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>粒子濃度が異常に高いな……呼吸器への負担が懸念される</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>粒子への曝露が終わり、くしゃみの頻度が減少したな</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>粒子への曝露が終わり、くしゃみの頻度が減少したな。疲労が、まだ残っているようだな</t>
         </is>
       </c>
     </row>
@@ -6219,12 +9567,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>問題ない。現状、直接の脅威は確認できていない</t>
+          <t>気のせいの可能性が高い。問題ないだろう</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>近くにいれば、脅威度は下がるはずだ</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>これは……本気で警戒すべきレベルの音だな</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>夜間の音源、朝になって観測されなくなったな……記録しておこう</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>夜間の音源、朝になって観測されなくなったな……記録しておこう。疲労が、まだ残っているようだな</t>
         </is>
       </c>
     </row>
@@ -6244,12 +9607,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>無害な種である可能性が高い。気にする必要はない</t>
+          <t>この程度の遭遇率なら、問題ないだろう</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>意識しなければ、支障はないはずだ</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>生理的嫌悪反応が強く出ているな……これは睡眠を妨げるレベルだ</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>昆虫の再出現は確認されていないな</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>昆虫の再出現は確認されていないな。疲労が、まだ残っているようだな</t>
         </is>
       </c>
     </row>
@@ -6269,12 +9647,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>警戒を怠るな。可能性を排除するのは早計だ</t>
+          <t>気のせいの可能性が高い。問題ないだろう</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>警戒していれば、対応できるはずだ</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>この感覚、無視できるレベルではないな……本格的に警戒すべきだ</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>夜間の異常な視線感知、朝には解消されているな</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>夜間の異常な視線感知、朝には解消されているな。疲労が、まだ残っているようだな</t>
         </is>
       </c>
     </row>
@@ -6294,12 +9687,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>構造的な軋み音の可能性が高い。脅威度は低いと判断する</t>
+          <t>この程度の音なら、睡眠には支障ないだろう</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>構造上の軋み音の可能性が高い。問題ないはずだ</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>この周期音、思考を妨げるレベルだな……看過できない</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>周期的発生音、日中は観測されないな……記録として残しておこう</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>周期的発生音、日中は観測されないな……記録として残しておこう。疲労が、まだ残っているようだな</t>
         </is>
       </c>
     </row>
@@ -6319,12 +9727,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>自己の外観を確認する機会など、久しくなかったな</t>
+          <t>統計的に珍しいだけだろう。問題ないはずだ</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>意識しなければ、支障はないはずだ</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>この保存状態、不自然だな……何らかの要因を疑うべきだ</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>日中の光の下で、改めて外観を確認しておくか</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>日中の光の下で、改めて外観を確認しておくか。疲労が、まだ残っているようだな</t>
         </is>
       </c>
     </row>
@@ -6339,17 +9762,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>見張りの順序を効率的に決める必要があるな。提案がある</t>
+          <t>気配を抑えていれば、発見されるリスクは低いはずだ</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>合理的な順序だ。異論はない</t>
+          <t>交代制にしよう。ボクが最初の番でも構わない</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>見張りのローテーション、問題なく機能したな</t>
+          <t>順序を、事前に決めておくべきだな</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>見張りは、非効率的に感じるが……仕方ないか</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>見張り任務、支障なく完了したな</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>睡眠時間が不足しているな……集中力の低下が懸念される</t>
         </is>
       </c>
     </row>
@@ -6364,17 +9802,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>均等な配分を計算するのは、意外と手間がかかるな</t>
+          <t>何を食べるか、決めておくか</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>ボクの分は最低限でいい。効率を優先しろ</t>
+          <t>この程度の量でも、必要最低限は満たすだろう</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>均等な配分であれば、問題はないはずだ</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>この量では、カロリー摂取量が明らかに不足するな……深刻だ</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>配分は、概ね公平だったと評価できるな</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>配分は、概ね公平だったと評価できるな。疲労が、まだ残っているようだな</t>
         </is>
       </c>
     </row>
@@ -6389,17 +9842,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>音量を抑える必要があるな。周囲に気取られないように</t>
+          <t>発生音を、最小限に抑える必要があるな</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>了解した。音量を調整する</t>
+          <t>この程度の音量制限なら、問題ないだろう</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>注意していれば、支障はないはずだ</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>継続的な音量抑制は、心理的ストレスを蓄積させるな</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>音量制限を解除できるな。日中は問題ない</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>音量制限を解除できるな。日中は問題ない。疲労が、まだ残っているようだな</t>
         </is>
       </c>
     </row>
@@ -6414,17 +9882,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>利用可能な平面が限られているな……体温共有が合理的だ</t>
+          <t>気温が低下しているな……保温手段を検討すべきか</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>非効率だが、ボクは端で構わない</t>
+          <t>この程度の気温なら、体温調節の範囲内だろう</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>体温を共有すれば、保温効果が見込める</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>この気温では、低体温症のリスクがあるな……深刻だ</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>体温共有は、予想以上に効果的だったな</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>体温共有は、予想以上に効果的だったな。疲労が、まだ残っているようだな</t>
         </is>
       </c>
     </row>
@@ -6444,12 +9927,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>好都合すぎる状況は、むしろ警戒すべきだな</t>
+          <t>この程度の保存状態は、稀だが説明可能な範囲だ</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>良好な拠点が見つかったのは、幸運だな</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>この完全性は統計的に異常だな……罠の可能性を精査すべきだ</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>結果として、警戒は杞憂に終わったな。悪いことではない</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>結果として、警戒は杞憂に終わったな。悪いことではない。疲労が、まだ残っているようだな</t>
         </is>
       </c>
     </row>
